--- a/docs/assets/assets/afl_fixtures_2026.xlsx
+++ b/docs/assets/assets/afl_fixtures_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DC17BC-72F1-42A1-965D-5D66204FB796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD6DF45-BDF8-4AEA-9124-1E24E53366A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22725" yWindow="1995" windowWidth="24465" windowHeight="12120" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/docs/assets/assets/afl_fixtures_2026.xlsx
+++ b/docs/assets/assets/afl_fixtures_2026.xlsx
@@ -6525,25 +6525,25 @@
         <v>652</v>
       </c>
       <c r="C140" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="D140" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="E140" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="F140" t="s">
-        <v>49</v>
+        <v>301</v>
       </c>
       <c r="G140" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H140" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I140" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="141" spans="1:9" ns3:dyDescent="0.25">
@@ -6557,22 +6557,22 @@
         <v>665</v>
       </c>
       <c r="D141" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E141" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="F141" t="s">
-        <v>301</v>
+        <v>49</v>
       </c>
       <c r="G141" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H141" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I141" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="142" spans="1:9" ns3:dyDescent="0.25">
@@ -6583,25 +6583,25 @@
         <v>652</v>
       </c>
       <c r="C142" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="D142" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="E142" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F142" t="s">
         <v>301</v>
       </c>
       <c r="G142" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H142" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I142" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="143" spans="1:9" ns3:dyDescent="0.25">
@@ -6612,25 +6612,25 @@
         <v>652</v>
       </c>
       <c r="C143" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="D143" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="E143" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F143" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G143" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="H143" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I143" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="144" spans="1:9" ns3:dyDescent="0.25">
@@ -6641,25 +6641,25 @@
         <v>652</v>
       </c>
       <c r="C144" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="D144" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E144" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="F144" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G144" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="H144" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I144" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="145" spans="1:9" ns3:dyDescent="0.25">
@@ -6699,25 +6699,25 @@
         <v>653</v>
       </c>
       <c r="C146" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D146" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E146" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F146" t="s">
-        <v>49</v>
+        <v>311</v>
       </c>
       <c r="G146" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="H146" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I146" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="147" spans="1:9" ns3:dyDescent="0.25">
@@ -6728,25 +6728,25 @@
         <v>653</v>
       </c>
       <c r="C147" t="s">
-        <v>675</v>
+        <v>649</v>
       </c>
       <c r="D147" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F147" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="G147" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H147" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="I147" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="148" spans="1:9" ns3:dyDescent="0.25">
@@ -6757,25 +6757,25 @@
         <v>653</v>
       </c>
       <c r="C148" t="s">
-        <v>664</v>
+        <v>649</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="E148" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="F148" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G148" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="H148" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I148" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="149" spans="1:9" ns3:dyDescent="0.25">
@@ -6789,22 +6789,22 @@
         <v>664</v>
       </c>
       <c r="D149" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="E149" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="F149" t="s">
-        <v>177</v>
+        <v>316</v>
       </c>
       <c r="G149" t="s">
-        <v>644</v>
+        <v>50</v>
       </c>
       <c r="H149" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I149" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="150" spans="1:9" ns3:dyDescent="0.25">
@@ -6818,22 +6818,22 @@
         <v>664</v>
       </c>
       <c r="D150" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="E150" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="F150" t="s">
-        <v>316</v>
+        <v>177</v>
       </c>
       <c r="G150" t="s">
-        <v>50</v>
+        <v>644</v>
       </c>
       <c r="H150" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I150" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="151" spans="1:9" ns3:dyDescent="0.25">
@@ -6847,22 +6847,22 @@
         <v>664</v>
       </c>
       <c r="D151" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="E151" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F151" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="G151" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H151" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I151" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="152" spans="1:9" ns3:dyDescent="0.25">
@@ -6873,25 +6873,25 @@
         <v>653</v>
       </c>
       <c r="C152" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="D152" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="E152" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="G152" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H152" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I152" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="153" spans="1:9" ns3:dyDescent="0.25">
@@ -6905,22 +6905,22 @@
         <v>671</v>
       </c>
       <c r="D153" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="E153" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="F153" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G153" t="s">
-        <v>178</v>
+        <v>69</v>
       </c>
       <c r="H153" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="I153" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
     </row>
     <row r="154" spans="1:9" ns3:dyDescent="0.25">
@@ -6931,25 +6931,25 @@
         <v>653</v>
       </c>
       <c r="C154" t="s">
-        <v>649</v>
+        <v>671</v>
       </c>
       <c r="D154" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E154" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="F154" t="s">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="G154" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H154" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I154" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="155" spans="1:9" ns3:dyDescent="0.25">
@@ -6960,25 +6960,25 @@
         <v>654</v>
       </c>
       <c r="C155" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="D155" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="E155" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="F155" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="G155" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H155" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="I155" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
     </row>
     <row r="156" spans="1:9" ns3:dyDescent="0.25">
@@ -6989,25 +6989,25 @@
         <v>654</v>
       </c>
       <c r="C156" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
       <c r="D156" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E156" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="F156" t="s">
-        <v>301</v>
+        <v>49</v>
       </c>
       <c r="G156" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H156" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I156" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="157" spans="1:9" ns3:dyDescent="0.25">
@@ -7018,25 +7018,25 @@
         <v>654</v>
       </c>
       <c r="C157" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="D157" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="E157" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F157" t="s">
         <v>49</v>
       </c>
       <c r="G157" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H157" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I157" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="158" spans="1:9" ns3:dyDescent="0.25">
@@ -7076,25 +7076,25 @@
         <v>654</v>
       </c>
       <c r="C159" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="D159" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E159" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F159" t="s">
         <v>301</v>
       </c>
       <c r="G159" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="H159" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I159" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="160" spans="1:9" ns3:dyDescent="0.25">
@@ -7108,22 +7108,22 @@
         <v>661</v>
       </c>
       <c r="D160" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="E160" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="F160" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G160" t="s">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="H160" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I160" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="161" spans="1:9" ns3:dyDescent="0.25">
@@ -7163,25 +7163,25 @@
         <v>654</v>
       </c>
       <c r="C162" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="D162" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E162" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="F162" t="s">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="G162" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="H162" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I162" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="163" spans="1:9" ns3:dyDescent="0.25">
@@ -7192,25 +7192,25 @@
         <v>654</v>
       </c>
       <c r="C163" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="D163" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="E163" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F163" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="G163" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H163" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="I163" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
     </row>
     <row r="164" spans="1:9" ns3:dyDescent="0.25">
@@ -7221,25 +7221,25 @@
         <v>655</v>
       </c>
       <c r="C164" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="D164" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E164" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="F164" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="G164" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H164" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I164" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="165" spans="1:9" ns3:dyDescent="0.25">
@@ -7250,25 +7250,25 @@
         <v>655</v>
       </c>
       <c r="C165" t="s">
-        <v>669</v>
+        <v>647</v>
       </c>
       <c r="D165" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F165" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="G165" t="s">
-        <v>178</v>
+        <v>44</v>
       </c>
       <c r="H165" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="I165" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="166" spans="1:9" ns3:dyDescent="0.25">
@@ -7279,25 +7279,25 @@
         <v>655</v>
       </c>
       <c r="C166" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="D166" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="E166" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F166" t="s">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="G166" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H166" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I166" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="167" spans="1:9" ns3:dyDescent="0.25">
@@ -7308,25 +7308,25 @@
         <v>655</v>
       </c>
       <c r="C167" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="D167" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="E167" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="F167" t="s">
-        <v>313</v>
+        <v>49</v>
       </c>
       <c r="G167" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="H167" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I167" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="168" spans="1:9" ns3:dyDescent="0.25">
@@ -7340,22 +7340,22 @@
         <v>662</v>
       </c>
       <c r="D168" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E168" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="F168" t="s">
-        <v>49</v>
+        <v>301</v>
       </c>
       <c r="G168" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H168" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I168" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="169" spans="1:9" ns3:dyDescent="0.25">
@@ -7366,25 +7366,25 @@
         <v>655</v>
       </c>
       <c r="C169" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="D169" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E169" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F169" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G169" t="s">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="H169" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I169" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="170" spans="1:9" ns3:dyDescent="0.25">
@@ -7395,25 +7395,25 @@
         <v>655</v>
       </c>
       <c r="C170" t="s">
-        <v>647</v>
+        <v>669</v>
       </c>
       <c r="D170" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="E170" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="F170" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="G170" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="H170" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I170" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="171" spans="1:9" ns3:dyDescent="0.25">
@@ -7424,25 +7424,25 @@
         <v>655</v>
       </c>
       <c r="C171" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="D171" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="E171" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F171" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="G171" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H171" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I171" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="172" spans="1:9" ns3:dyDescent="0.25">
@@ -7453,25 +7453,25 @@
         <v>655</v>
       </c>
       <c r="C172" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="D172" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="E172" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F172" t="s">
-        <v>306</v>
+        <v>49</v>
       </c>
       <c r="G172" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H172" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="I172" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="173" spans="1:9" ns3:dyDescent="0.25">
@@ -7482,25 +7482,25 @@
         <v>656</v>
       </c>
       <c r="C173" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="D173" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="E173" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F173" t="s">
-        <v>298</v>
+        <v>81</v>
       </c>
       <c r="G173" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="H173" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="I173" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="174" spans="1:9" ns3:dyDescent="0.25">
@@ -7511,25 +7511,25 @@
         <v>656</v>
       </c>
       <c r="C174" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="D174" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E174" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="F174" t="s">
-        <v>49</v>
+        <v>301</v>
       </c>
       <c r="G174" t="s">
-        <v>643</v>
+        <v>44</v>
       </c>
       <c r="H174" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I174" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="175" spans="1:9" ns3:dyDescent="0.25">
@@ -7540,25 +7540,25 @@
         <v>656</v>
       </c>
       <c r="C175" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="D175" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="E175" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F175" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="G175" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H175" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I175" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="176" spans="1:9" ns3:dyDescent="0.25">
@@ -7572,22 +7572,22 @@
         <v>663</v>
       </c>
       <c r="D176" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="E176" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F176" t="s">
-        <v>301</v>
+        <v>49</v>
       </c>
       <c r="G176" t="s">
-        <v>24</v>
+        <v>643</v>
       </c>
       <c r="H176" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I176" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="177" spans="1:9" ns3:dyDescent="0.25">
@@ -7598,25 +7598,25 @@
         <v>656</v>
       </c>
       <c r="C177" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="D177" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E177" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="F177" t="s">
-        <v>49</v>
+        <v>301</v>
       </c>
       <c r="G177" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="H177" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I177" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="178" spans="1:9" ns3:dyDescent="0.25">
@@ -7627,25 +7627,25 @@
         <v>656</v>
       </c>
       <c r="C178" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="D178" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E178" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="F178" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="G178" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="H178" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I178" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="179" spans="1:9" ns3:dyDescent="0.25">
@@ -7685,25 +7685,25 @@
         <v>656</v>
       </c>
       <c r="C180" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D180" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="E180" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F180" t="s">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="G180" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="H180" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I180" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
     </row>
     <row r="181" spans="1:9" ns3:dyDescent="0.25">
@@ -7714,25 +7714,25 @@
         <v>656</v>
       </c>
       <c r="C181" t="s">
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="D181" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="E181" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F181" t="s">
-        <v>306</v>
+        <v>49</v>
       </c>
       <c r="G181" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="H181" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I181" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="182" spans="1:9" ns3:dyDescent="0.25">
@@ -7743,25 +7743,25 @@
         <v>657</v>
       </c>
       <c r="C182" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="D182" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E182" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F182" t="s">
-        <v>49</v>
+        <v>301</v>
       </c>
       <c r="G182" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H182" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I182" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="183" spans="1:9" ns3:dyDescent="0.25">
@@ -7772,25 +7772,25 @@
         <v>657</v>
       </c>
       <c r="C183" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D183" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="E183" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F183" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G183" t="s">
-        <v>12</v>
+        <v>185</v>
       </c>
       <c r="H183" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="I183" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="184" spans="1:9" ns3:dyDescent="0.25">
@@ -7801,25 +7801,25 @@
         <v>657</v>
       </c>
       <c r="C184" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="D184" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E184" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F184" t="s">
         <v>49</v>
       </c>
       <c r="G184" t="s">
-        <v>178</v>
+        <v>643</v>
       </c>
       <c r="H184" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I184" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="185" spans="1:9" ns3:dyDescent="0.25">
@@ -7830,25 +7830,25 @@
         <v>657</v>
       </c>
       <c r="C185" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="D185" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E185" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F185" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G185" t="s">
-        <v>69</v>
+        <v>644</v>
       </c>
       <c r="H185" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I185" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="186" spans="1:9" ns3:dyDescent="0.25">
@@ -7862,22 +7862,22 @@
         <v>659</v>
       </c>
       <c r="D186" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E186" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="F186" t="s">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="G186" t="s">
-        <v>644</v>
+        <v>170</v>
       </c>
       <c r="H186" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I186" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="187" spans="1:9" ns3:dyDescent="0.25">
@@ -7888,25 +7888,25 @@
         <v>657</v>
       </c>
       <c r="C187" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="D187" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="E187" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F187" t="s">
-        <v>301</v>
+        <v>49</v>
       </c>
       <c r="G187" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="H187" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="I187" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="188" spans="1:9" ns3:dyDescent="0.25">
@@ -7917,25 +7917,25 @@
         <v>657</v>
       </c>
       <c r="C188" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="D188" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="E188" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F188" t="s">
-        <v>49</v>
+        <v>301</v>
       </c>
       <c r="G188" t="s">
-        <v>643</v>
+        <v>65</v>
       </c>
       <c r="H188" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I188" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="189" spans="1:9" ns3:dyDescent="0.25">
@@ -7946,25 +7946,25 @@
         <v>657</v>
       </c>
       <c r="C189" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="D189" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="E189" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="F189" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="G189" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="H189" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="I189" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="190" spans="1:9" ns3:dyDescent="0.25">
@@ -7975,25 +7975,25 @@
         <v>657</v>
       </c>
       <c r="C190" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="D190" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="E190" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="F190" t="s">
-        <v>306</v>
+        <v>49</v>
       </c>
       <c r="G190" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H190" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="I190" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="191" spans="1:9" ns3:dyDescent="0.25">
@@ -8004,25 +8004,25 @@
         <v>658</v>
       </c>
       <c r="C191" t="s">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="D191" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E191" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="F191" t="s">
-        <v>298</v>
+        <v>49</v>
       </c>
       <c r="G191" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H191" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="I191" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="192" spans="1:9" ns3:dyDescent="0.25">
@@ -8033,25 +8033,25 @@
         <v>658</v>
       </c>
       <c r="C192" t="s">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="D192" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="E192" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="F192" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="G192" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="H192" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I192" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="193" spans="1:9" ns3:dyDescent="0.25">
@@ -8062,25 +8062,25 @@
         <v>658</v>
       </c>
       <c r="C193" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="D193" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E193" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="F193" t="s">
-        <v>177</v>
+        <v>301</v>
       </c>
       <c r="G193" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H193" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I193" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="194" spans="1:9" ns3:dyDescent="0.25">
@@ -8094,22 +8094,22 @@
         <v>660</v>
       </c>
       <c r="D194" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E194" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F194" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="G194" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="H194" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I194" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="195" spans="1:9" ns3:dyDescent="0.25">
@@ -8120,25 +8120,25 @@
         <v>658</v>
       </c>
       <c r="C195" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="D195" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E195" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="F195" t="s">
-        <v>49</v>
+        <v>311</v>
       </c>
       <c r="G195" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="H195" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I195" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="196" spans="1:9" ns3:dyDescent="0.25">
@@ -8152,22 +8152,22 @@
         <v>660</v>
       </c>
       <c r="D196" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="E196" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="F196" t="s">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="G196" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H196" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I196" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="197" spans="1:9" ns3:dyDescent="0.25">
@@ -8178,25 +8178,25 @@
         <v>658</v>
       </c>
       <c r="C197" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D197" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E197" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F197" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="G197" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="H197" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I197" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="198" spans="1:9" ns3:dyDescent="0.25">
@@ -8207,25 +8207,25 @@
         <v>658</v>
       </c>
       <c r="C198" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="D198" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E198" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F198" t="s">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="G198" t="s">
-        <v>29</v>
+        <v>407</v>
       </c>
       <c r="H198" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I198" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="199" spans="1:9" ns3:dyDescent="0.25">
@@ -8239,22 +8239,22 @@
         <v>667</v>
       </c>
       <c r="D199" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="E199" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F199" t="s">
-        <v>306</v>
+        <v>49</v>
       </c>
       <c r="G199" t="s">
-        <v>407</v>
+        <v>35</v>
       </c>
       <c r="H199" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="I199" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="200" spans="1:9" ns3:dyDescent="0.25">

--- a/docs/assets/assets/afl_fixtures_2026.xlsx
+++ b/docs/assets/assets/afl_fixtures_2026.xlsx
@@ -36,2093 +36,2093 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="695">
-  <ns0:si>
-    <ns0:t>ROUND</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>DATE</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>HOME TEAM</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>AWAY TEAM</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>VENUE</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>TIME</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>GAME DATA SOURCE</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>OPENING ROUND</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday March 5</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sydney Swans </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Carlton</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> SCG </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7.30pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8041</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday March 6</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Gold Coast Suns </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Geelong Cats</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> People First Stadium </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>8.05pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8042</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday March 7</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>GWS Giants </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Hawthorn</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> ENGIE Stadium </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8040</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Brisbane Lions </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Western Bulldogs</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> The Gabba </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7.35pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8043</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday March 8</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>St Kilda </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Collingwood</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> MCG </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7.20pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8046</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday March 12</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Carlton </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Richmond</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8045</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday March 13</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Essendon </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7.40pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8044</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday March 14</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Western Bulldogs </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> GWS Giants</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Marvel Stadium</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8047</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Geelong Cats </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Fremantle</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> GMHBA Stadium </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8049</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Brisbane Lions</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7.10pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8048</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Collingwood </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Adelaide Crows</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8051</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday March 15</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>North Melbourne </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Port Adelaide</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1.10pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8056</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Melbourne </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> St Kilda</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8055</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> West Coast Eagles</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>6.10pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8050</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday March 19</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Hawthorn </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Sydney Swans</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8052</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday March 20</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Adelaide Crows </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Adelaide Oval</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8053</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday March 21</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Richmond </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Gold Coast Suns</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8054</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8059</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Fremantle </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Melbourne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Optus Stadium </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8057</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday March 22</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Port Adelaide </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Essendon</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8058</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>West Coast Eagles </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> North Melbourne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8060</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 3</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday March 26</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8062</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday March 27</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8064</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday March 28</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>12.35pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8061</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8065</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8063</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday March 29</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>12.30pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8071</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8075</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 4</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday April 2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8066</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday April 3</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8067</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8069</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday April 4</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8070</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8068</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday April 5</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8074</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8073</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Monday April 6</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8077</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 5</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday April 9</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8072</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday April 10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8076</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday April 11</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Barossa Park </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8078</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8079</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Norwood Oval</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8080</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8081</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday April 12</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8082</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8084</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8088</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 6</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday April 16</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8083</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday April 17</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8085</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7.50pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8086</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday April 18</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8087</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8089</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8092</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday April 19</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8090</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8091</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>5.10pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8094</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 7</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday April 23</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8093</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday April 24</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8097</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday April 25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> UTAS Stadium </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>12.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8095</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8098</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>6.35pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8096</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>8.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8105</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday April 26</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8100</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8099</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Corroboree Group Oval Manuka</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4.40pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8101</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 8</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday April 30</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8104</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday May 1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8102</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>8.10pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8103</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday May 2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8109</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8108</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4.35pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8106</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8114</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday May 3</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8107</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8111</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 9</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday May 7</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8113</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday May 8</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8116</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8110</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday May 9</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8112</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8115</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> TIO Stadium </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8120</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8119</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday May 10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8122</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8118</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday May 14</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8117</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday May 15</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8121</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8125</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday May 16</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8124</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8129</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8123</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday May 17</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8126</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8127</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>6.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8128</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 11</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday May 21</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8130</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday May 22</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8131</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>8.30pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8133</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday May 23</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8134</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8132</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8137</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8135</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday May 24</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8136</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8138</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 12</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday May 28</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8139</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday May 29</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8140</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday May 30</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8141</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8142</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8143</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday May 31</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> TIO Traeger Park Oval</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8144</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8145</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 13</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday June 4</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8148</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday June 5</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8146</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday June 6</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Hands Oval</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8147</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>5.15pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8150</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8149</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday June 7</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8152</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8151</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Monday June 8</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8153</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 14</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday June 11</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8154</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday June 12</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8158</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday June 13</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8156</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8155</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8157</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday June 14</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Ninja Stadium </ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8159</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8170</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 15</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday June 18</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8160</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday June 19</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8161</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday June 20</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8164</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8162</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8163</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday June 21</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8165</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8166</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 16 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday June 25 – Sunday June 28</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> The Gabba</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8168</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8167</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> MCG</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8174</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8172</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8169</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8179</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> Optus Stadium</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8171</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 17 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 2 – Sunday July 5</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8173</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> GMHBA Stadium</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8178</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> People First Stadium</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8180</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8187</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> UTAS Stadium</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8175</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8176</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> SCG</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8177</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8181</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8183</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 18 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 9 – Sunday July 12</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8186</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8184</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8182</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t> ENGIE Stadium</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8192</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8185</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8188</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8193</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8190</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8189</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 19 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 16 – Sunday July 19</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8194</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8191</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8195</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8200</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8197</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8196</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8199</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8198</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8202</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 20 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 23 – Sunday July 26</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8203</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8201</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8208</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8206</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8207</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8205</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8204</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8216</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8210</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 21 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 30 – Sunday August 2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8209</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8213</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8211</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8215</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8212</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8214</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8217</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8221</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8218</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 22 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday August 6 – Sunday August 9</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8223</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8219</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8228</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8220</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8225</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8222</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8224</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8230</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8227</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 23 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday August 13 – Sunday August 16</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8229</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8226</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8233</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8244</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8231</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8238</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8232</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8234</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8237</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 24 (dates and times TBC)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday August 20 – Sunday August 23</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8239</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8240</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8235</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8246</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8236</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8242</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8245</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8243</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8241</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Match ID</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Wednesday February 25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>IKON Park</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8251</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday February 26</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Henson Park</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4.10pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8250</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Brighton Homes Arena</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8252</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday February 27</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Mars Stadium</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8255</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Mission Whitten Oval</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8253</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday February 28</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3.10pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8254</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Rushton Park</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8256</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday March 1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8257</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Mineral Resources Park</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>https://www.afl.com.au/afl/matches/8258</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Pre-Season</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140001</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140002</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140003</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140004</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140005</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140101</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140102</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140103</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140104</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140105</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140106</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140107</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140108</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140109</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140201</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140202</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140203</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140204</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140205</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140206</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140207</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140301</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140302</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140303</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140304</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140305</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140306</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140307</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140401</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140402</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140403</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140404</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140405</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140406</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140407</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140408</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140501</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140502</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140503</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140504</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140505</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140506</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140507</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140508</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140509</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140601</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140602</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140603</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140604</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140605</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140606</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140607</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140608</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140609</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140701</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140702</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140703</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140704</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140705</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140706</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140707</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140708</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140709</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140801</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140802</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140803</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140804</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140805</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140806</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140807</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140808</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140809</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140901</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140902</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140903</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140904</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140905</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140906</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140907</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140908</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260140909</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141001</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141002</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141003</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141004</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141005</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141006</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141007</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141008</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141009</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141101</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141102</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141103</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141104</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141105</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141106</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141107</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141108</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141109</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141201</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141202</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141203</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141204</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141205</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141206</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141207</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141301</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141302</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141303</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141304</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141305</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141306</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141307</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141308</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141401</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141402</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141403</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141404</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141405</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141406</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141407</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141501</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141502</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141503</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141504</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141505</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141506</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141507</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141601</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141602</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141603</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141605</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141606</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141607</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141604</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141701</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141702</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141703</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141704</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141705</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141707</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141708</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141706</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141709</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141802</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141803</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141804</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141806</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141807</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141808</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141809</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141801</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141805</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141901</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141902</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141903</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141904</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141905</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141907</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141908</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141906</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260141909</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142002</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142003</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142005</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142006</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142007</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142008</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142009</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142001</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142004</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142101</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142102</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142103</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142105</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142106</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142108</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142109</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142107</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142104</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142202</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142203</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142204</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142205</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142206</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142207</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142209</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142201</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142208</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142301</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142302</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142304</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142305</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142306</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142308</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142309</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142307</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142303</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142402</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142403</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142404</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142405</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142406</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142407</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142408</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142401</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20260142409</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010101</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010102</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010103</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010104</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010105</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010106</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010107</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010108</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>CD_M20261010109</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>SEASON</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1.05pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1.35pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday August 7</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday July 10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday July 17</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday July 24</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday July 3</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday July 31</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday June 26</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 16</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 17</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 18</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 19</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 20</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 21</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 22</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday August 1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday August 8</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday July 11</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday July 18</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday July 25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday July 4</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday June 27</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday August 2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday August 9</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday July 12</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday July 19</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday July 26</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday July 5</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday June 28</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday August 6</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 16</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 23</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 30</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday July 9</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday June 25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 23</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday August 15</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday August 16</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1.40pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3.45pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>9.10pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday August 14</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>ROUND 24</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Friday August 21</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Saturday August 22</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sunday August 23</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>12.20pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7.45pm</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Thursday August 20</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3.20pm</ns0:t>
-  </ns0:si>
-</ns0:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="695">
+  <si>
+    <t>ROUND</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>HOME TEAM</t>
+  </si>
+  <si>
+    <t>AWAY TEAM</t>
+  </si>
+  <si>
+    <t>VENUE</t>
+  </si>
+  <si>
+    <t>TIME</t>
+  </si>
+  <si>
+    <t>GAME DATA SOURCE</t>
+  </si>
+  <si>
+    <t>OPENING ROUND</t>
+  </si>
+  <si>
+    <t>Thursday March 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Swans </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SCG </t>
+  </si>
+  <si>
+    <t>7.30pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8041</t>
+  </si>
+  <si>
+    <t>Friday March 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Coast Suns </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Geelong Cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> People First Stadium </t>
+  </si>
+  <si>
+    <t>8.05pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8042</t>
+  </si>
+  <si>
+    <t>Saturday March 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWS Giants </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ENGIE Stadium </t>
+  </si>
+  <si>
+    <t>4.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Lions </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Western Bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The Gabba </t>
+  </si>
+  <si>
+    <t>7.35pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8043</t>
+  </si>
+  <si>
+    <t>Sunday March 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St Kilda </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MCG </t>
+  </si>
+  <si>
+    <t>7.20pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8046</t>
+  </si>
+  <si>
+    <t>ROUND 1</t>
+  </si>
+  <si>
+    <t>Thursday March 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlton </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Richmond</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8045</t>
+  </si>
+  <si>
+    <t>Friday March 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essendon </t>
+  </si>
+  <si>
+    <t>7.40pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8044</t>
+  </si>
+  <si>
+    <t>Saturday March 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Bulldogs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GWS Giants</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Marvel Stadium</t>
+  </si>
+  <si>
+    <t>1.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geelong Cats </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GMHBA Stadium </t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8049</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Brisbane Lions</t>
+  </si>
+  <si>
+    <t>7.10pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collingwood </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adelaide Crows</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8051</t>
+  </si>
+  <si>
+    <t>Sunday March 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Melbourne </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Port Adelaide</t>
+  </si>
+  <si>
+    <t>1.10pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melbourne </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> St Kilda</t>
+  </si>
+  <si>
+    <t>3.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8055</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Coast Eagles</t>
+  </si>
+  <si>
+    <t>6.10pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8050</t>
+  </si>
+  <si>
+    <t>ROUND 2</t>
+  </si>
+  <si>
+    <t>Thursday March 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawthorn </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sydney Swans</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8052</t>
+  </si>
+  <si>
+    <t>Friday March 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adelaide Crows </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adelaide Oval</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8053</t>
+  </si>
+  <si>
+    <t>Saturday March 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richmond </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gold Coast Suns</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8054</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fremantle </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Optus Stadium </t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8057</t>
+  </si>
+  <si>
+    <t>Sunday March 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port Adelaide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Essendon</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Coast Eagles </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> North Melbourne</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8060</t>
+  </si>
+  <si>
+    <t>ROUND 3</t>
+  </si>
+  <si>
+    <t>Thursday March 26</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8062</t>
+  </si>
+  <si>
+    <t>Friday March 27</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8064</t>
+  </si>
+  <si>
+    <t>Saturday March 28</t>
+  </si>
+  <si>
+    <t>12.35pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8061</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8065</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8063</t>
+  </si>
+  <si>
+    <t>Sunday March 29</t>
+  </si>
+  <si>
+    <t>12.30pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8071</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8075</t>
+  </si>
+  <si>
+    <t>ROUND 4</t>
+  </si>
+  <si>
+    <t>Thursday April 2</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8066</t>
+  </si>
+  <si>
+    <t>Friday April 3</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8067</t>
+  </si>
+  <si>
+    <t>7.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8069</t>
+  </si>
+  <si>
+    <t>Saturday April 4</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8070</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8068</t>
+  </si>
+  <si>
+    <t>Sunday April 5</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8074</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8073</t>
+  </si>
+  <si>
+    <t>Monday April 6</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8077</t>
+  </si>
+  <si>
+    <t>ROUND 5</t>
+  </si>
+  <si>
+    <t>Thursday April 9</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8072</t>
+  </si>
+  <si>
+    <t>Friday April 10</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8076</t>
+  </si>
+  <si>
+    <t>Saturday April 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Barossa Park </t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8078</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8079</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Norwood Oval</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8080</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8081</t>
+  </si>
+  <si>
+    <t>Sunday April 12</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8082</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8084</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8088</t>
+  </si>
+  <si>
+    <t>ROUND 6</t>
+  </si>
+  <si>
+    <t>Thursday April 16</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8083</t>
+  </si>
+  <si>
+    <t>Friday April 17</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8085</t>
+  </si>
+  <si>
+    <t>7.50pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8086</t>
+  </si>
+  <si>
+    <t>Saturday April 18</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8087</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8089</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8092</t>
+  </si>
+  <si>
+    <t>Sunday April 19</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8090</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8091</t>
+  </si>
+  <si>
+    <t>5.10pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8094</t>
+  </si>
+  <si>
+    <t>ROUND 7</t>
+  </si>
+  <si>
+    <t>Thursday April 23</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8093</t>
+  </si>
+  <si>
+    <t>Friday April 24</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8097</t>
+  </si>
+  <si>
+    <t>Saturday April 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UTAS Stadium </t>
+  </si>
+  <si>
+    <t>12.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8095</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8098</t>
+  </si>
+  <si>
+    <t>6.35pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8096</t>
+  </si>
+  <si>
+    <t>8.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8105</t>
+  </si>
+  <si>
+    <t>Sunday April 26</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8100</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8099</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Corroboree Group Oval Manuka</t>
+  </si>
+  <si>
+    <t>4.40pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8101</t>
+  </si>
+  <si>
+    <t>ROUND 8</t>
+  </si>
+  <si>
+    <t>Thursday April 30</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8104</t>
+  </si>
+  <si>
+    <t>Friday May 1</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8102</t>
+  </si>
+  <si>
+    <t>8.10pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8103</t>
+  </si>
+  <si>
+    <t>Saturday May 2</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8109</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8108</t>
+  </si>
+  <si>
+    <t>4.35pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8106</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8114</t>
+  </si>
+  <si>
+    <t>Sunday May 3</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8107</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8111</t>
+  </si>
+  <si>
+    <t>ROUND 9</t>
+  </si>
+  <si>
+    <t>Thursday May 7</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8113</t>
+  </si>
+  <si>
+    <t>Friday May 8</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8116</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8110</t>
+  </si>
+  <si>
+    <t>Saturday May 9</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8112</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8115</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIO Stadium </t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8120</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8119</t>
+  </si>
+  <si>
+    <t>Sunday May 10</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8122</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8118</t>
+  </si>
+  <si>
+    <t>ROUND 10</t>
+  </si>
+  <si>
+    <t>Thursday May 14</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8117</t>
+  </si>
+  <si>
+    <t>Friday May 15</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8121</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8125</t>
+  </si>
+  <si>
+    <t>Saturday May 16</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8124</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8129</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8123</t>
+  </si>
+  <si>
+    <t>Sunday May 17</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8126</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8127</t>
+  </si>
+  <si>
+    <t>6.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8128</t>
+  </si>
+  <si>
+    <t>ROUND 11</t>
+  </si>
+  <si>
+    <t>Thursday May 21</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8130</t>
+  </si>
+  <si>
+    <t>Friday May 22</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8131</t>
+  </si>
+  <si>
+    <t>8.30pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8133</t>
+  </si>
+  <si>
+    <t>Saturday May 23</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8134</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8132</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8137</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8135</t>
+  </si>
+  <si>
+    <t>Sunday May 24</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8136</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8138</t>
+  </si>
+  <si>
+    <t>ROUND 12</t>
+  </si>
+  <si>
+    <t>Thursday May 28</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8139</t>
+  </si>
+  <si>
+    <t>Friday May 29</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8140</t>
+  </si>
+  <si>
+    <t>Saturday May 30</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8141</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8142</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8143</t>
+  </si>
+  <si>
+    <t>Sunday May 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIO Traeger Park Oval</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8144</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8145</t>
+  </si>
+  <si>
+    <t>ROUND 13</t>
+  </si>
+  <si>
+    <t>Thursday June 4</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8148</t>
+  </si>
+  <si>
+    <t>Friday June 5</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8146</t>
+  </si>
+  <si>
+    <t>Saturday June 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hands Oval</t>
+  </si>
+  <si>
+    <t>2.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8147</t>
+  </si>
+  <si>
+    <t>5.15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8150</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8149</t>
+  </si>
+  <si>
+    <t>Sunday June 7</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8152</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8151</t>
+  </si>
+  <si>
+    <t>Monday June 8</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8153</t>
+  </si>
+  <si>
+    <t>ROUND 14</t>
+  </si>
+  <si>
+    <t>Thursday June 11</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8154</t>
+  </si>
+  <si>
+    <t>Friday June 12</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8158</t>
+  </si>
+  <si>
+    <t>Saturday June 13</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8156</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8155</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8157</t>
+  </si>
+  <si>
+    <t>Sunday June 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ninja Stadium </t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8159</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8170</t>
+  </si>
+  <si>
+    <t>ROUND 15</t>
+  </si>
+  <si>
+    <t>Thursday June 18</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8160</t>
+  </si>
+  <si>
+    <t>Friday June 19</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8161</t>
+  </si>
+  <si>
+    <t>Saturday June 20</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8164</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8162</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8163</t>
+  </si>
+  <si>
+    <t>Sunday June 21</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8165</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8166</t>
+  </si>
+  <si>
+    <t>ROUND 16 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday June 25 – Sunday June 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The Gabba</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8168</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8167</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MCG</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8174</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8172</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8169</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8179</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Optus Stadium</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8171</t>
+  </si>
+  <si>
+    <t>ROUND 17 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday July 2 – Sunday July 5</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8173</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GMHBA Stadium</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8178</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> People First Stadium</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8180</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8187</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UTAS Stadium</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8175</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8176</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SCG</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8177</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8181</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8183</t>
+  </si>
+  <si>
+    <t>ROUND 18 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday July 9 – Sunday July 12</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8186</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8184</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8182</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ENGIE Stadium</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8192</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8185</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8188</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8193</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8190</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8189</t>
+  </si>
+  <si>
+    <t>ROUND 19 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday July 16 – Sunday July 19</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8194</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8191</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8195</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8200</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8197</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8196</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8199</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8198</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8202</t>
+  </si>
+  <si>
+    <t>ROUND 20 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday July 23 – Sunday July 26</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8203</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8201</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8208</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8206</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8207</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8205</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8204</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8216</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8210</t>
+  </si>
+  <si>
+    <t>ROUND 21 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday July 30 – Sunday August 2</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8209</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8213</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8211</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8215</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8212</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8214</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8217</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8221</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8218</t>
+  </si>
+  <si>
+    <t>ROUND 22 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday August 6 – Sunday August 9</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8223</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8219</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8228</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8220</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8225</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8222</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8224</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8230</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8227</t>
+  </si>
+  <si>
+    <t>ROUND 23 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday August 13 – Sunday August 16</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8229</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8226</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8233</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8244</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8231</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8238</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8232</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8234</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8237</t>
+  </si>
+  <si>
+    <t>ROUND 24 (dates and times TBC)</t>
+  </si>
+  <si>
+    <t>Thursday August 20 – Sunday August 23</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8239</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8240</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8235</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8246</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8236</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8242</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8245</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8243</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8241</t>
+  </si>
+  <si>
+    <t>Match ID</t>
+  </si>
+  <si>
+    <t>Wednesday February 25</t>
+  </si>
+  <si>
+    <t>IKON Park</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8251</t>
+  </si>
+  <si>
+    <t>Thursday February 26</t>
+  </si>
+  <si>
+    <t>Henson Park</t>
+  </si>
+  <si>
+    <t>4.10pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8250</t>
+  </si>
+  <si>
+    <t>Brighton Homes Arena</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8252</t>
+  </si>
+  <si>
+    <t>Friday February 27</t>
+  </si>
+  <si>
+    <t>Mars Stadium</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8255</t>
+  </si>
+  <si>
+    <t>Mission Whitten Oval</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8253</t>
+  </si>
+  <si>
+    <t>Saturday February 28</t>
+  </si>
+  <si>
+    <t>3.10pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8254</t>
+  </si>
+  <si>
+    <t>Rushton Park</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8256</t>
+  </si>
+  <si>
+    <t>Sunday March 1</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8257</t>
+  </si>
+  <si>
+    <t>Mineral Resources Park</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/8258</t>
+  </si>
+  <si>
+    <t>Pre-Season</t>
+  </si>
+  <si>
+    <t>CD_M20260140001</t>
+  </si>
+  <si>
+    <t>CD_M20260140002</t>
+  </si>
+  <si>
+    <t>CD_M20260140003</t>
+  </si>
+  <si>
+    <t>CD_M20260140004</t>
+  </si>
+  <si>
+    <t>CD_M20260140005</t>
+  </si>
+  <si>
+    <t>CD_M20260140101</t>
+  </si>
+  <si>
+    <t>CD_M20260140102</t>
+  </si>
+  <si>
+    <t>CD_M20260140103</t>
+  </si>
+  <si>
+    <t>CD_M20260140104</t>
+  </si>
+  <si>
+    <t>CD_M20260140105</t>
+  </si>
+  <si>
+    <t>CD_M20260140106</t>
+  </si>
+  <si>
+    <t>CD_M20260140107</t>
+  </si>
+  <si>
+    <t>CD_M20260140108</t>
+  </si>
+  <si>
+    <t>CD_M20260140109</t>
+  </si>
+  <si>
+    <t>CD_M20260140201</t>
+  </si>
+  <si>
+    <t>CD_M20260140202</t>
+  </si>
+  <si>
+    <t>CD_M20260140203</t>
+  </si>
+  <si>
+    <t>CD_M20260140204</t>
+  </si>
+  <si>
+    <t>CD_M20260140205</t>
+  </si>
+  <si>
+    <t>CD_M20260140206</t>
+  </si>
+  <si>
+    <t>CD_M20260140207</t>
+  </si>
+  <si>
+    <t>CD_M20260140301</t>
+  </si>
+  <si>
+    <t>CD_M20260140302</t>
+  </si>
+  <si>
+    <t>CD_M20260140303</t>
+  </si>
+  <si>
+    <t>CD_M20260140304</t>
+  </si>
+  <si>
+    <t>CD_M20260140305</t>
+  </si>
+  <si>
+    <t>CD_M20260140306</t>
+  </si>
+  <si>
+    <t>CD_M20260140307</t>
+  </si>
+  <si>
+    <t>CD_M20260140401</t>
+  </si>
+  <si>
+    <t>CD_M20260140402</t>
+  </si>
+  <si>
+    <t>CD_M20260140403</t>
+  </si>
+  <si>
+    <t>CD_M20260140404</t>
+  </si>
+  <si>
+    <t>CD_M20260140405</t>
+  </si>
+  <si>
+    <t>CD_M20260140406</t>
+  </si>
+  <si>
+    <t>CD_M20260140407</t>
+  </si>
+  <si>
+    <t>CD_M20260140408</t>
+  </si>
+  <si>
+    <t>CD_M20260140501</t>
+  </si>
+  <si>
+    <t>CD_M20260140502</t>
+  </si>
+  <si>
+    <t>CD_M20260140503</t>
+  </si>
+  <si>
+    <t>CD_M20260140504</t>
+  </si>
+  <si>
+    <t>CD_M20260140505</t>
+  </si>
+  <si>
+    <t>CD_M20260140506</t>
+  </si>
+  <si>
+    <t>CD_M20260140507</t>
+  </si>
+  <si>
+    <t>CD_M20260140508</t>
+  </si>
+  <si>
+    <t>CD_M20260140509</t>
+  </si>
+  <si>
+    <t>CD_M20260140601</t>
+  </si>
+  <si>
+    <t>CD_M20260140602</t>
+  </si>
+  <si>
+    <t>CD_M20260140603</t>
+  </si>
+  <si>
+    <t>CD_M20260140604</t>
+  </si>
+  <si>
+    <t>CD_M20260140605</t>
+  </si>
+  <si>
+    <t>CD_M20260140606</t>
+  </si>
+  <si>
+    <t>CD_M20260140607</t>
+  </si>
+  <si>
+    <t>CD_M20260140608</t>
+  </si>
+  <si>
+    <t>CD_M20260140609</t>
+  </si>
+  <si>
+    <t>CD_M20260140701</t>
+  </si>
+  <si>
+    <t>CD_M20260140702</t>
+  </si>
+  <si>
+    <t>CD_M20260140703</t>
+  </si>
+  <si>
+    <t>CD_M20260140704</t>
+  </si>
+  <si>
+    <t>CD_M20260140705</t>
+  </si>
+  <si>
+    <t>CD_M20260140706</t>
+  </si>
+  <si>
+    <t>CD_M20260140707</t>
+  </si>
+  <si>
+    <t>CD_M20260140708</t>
+  </si>
+  <si>
+    <t>CD_M20260140709</t>
+  </si>
+  <si>
+    <t>CD_M20260140801</t>
+  </si>
+  <si>
+    <t>CD_M20260140802</t>
+  </si>
+  <si>
+    <t>CD_M20260140803</t>
+  </si>
+  <si>
+    <t>CD_M20260140804</t>
+  </si>
+  <si>
+    <t>CD_M20260140805</t>
+  </si>
+  <si>
+    <t>CD_M20260140806</t>
+  </si>
+  <si>
+    <t>CD_M20260140807</t>
+  </si>
+  <si>
+    <t>CD_M20260140808</t>
+  </si>
+  <si>
+    <t>CD_M20260140809</t>
+  </si>
+  <si>
+    <t>CD_M20260140901</t>
+  </si>
+  <si>
+    <t>CD_M20260140902</t>
+  </si>
+  <si>
+    <t>CD_M20260140903</t>
+  </si>
+  <si>
+    <t>CD_M20260140904</t>
+  </si>
+  <si>
+    <t>CD_M20260140905</t>
+  </si>
+  <si>
+    <t>CD_M20260140906</t>
+  </si>
+  <si>
+    <t>CD_M20260140907</t>
+  </si>
+  <si>
+    <t>CD_M20260140908</t>
+  </si>
+  <si>
+    <t>CD_M20260140909</t>
+  </si>
+  <si>
+    <t>CD_M20260141001</t>
+  </si>
+  <si>
+    <t>CD_M20260141002</t>
+  </si>
+  <si>
+    <t>CD_M20260141003</t>
+  </si>
+  <si>
+    <t>CD_M20260141004</t>
+  </si>
+  <si>
+    <t>CD_M20260141005</t>
+  </si>
+  <si>
+    <t>CD_M20260141006</t>
+  </si>
+  <si>
+    <t>CD_M20260141007</t>
+  </si>
+  <si>
+    <t>CD_M20260141008</t>
+  </si>
+  <si>
+    <t>CD_M20260141009</t>
+  </si>
+  <si>
+    <t>CD_M20260141101</t>
+  </si>
+  <si>
+    <t>CD_M20260141102</t>
+  </si>
+  <si>
+    <t>CD_M20260141103</t>
+  </si>
+  <si>
+    <t>CD_M20260141104</t>
+  </si>
+  <si>
+    <t>CD_M20260141105</t>
+  </si>
+  <si>
+    <t>CD_M20260141106</t>
+  </si>
+  <si>
+    <t>CD_M20260141107</t>
+  </si>
+  <si>
+    <t>CD_M20260141108</t>
+  </si>
+  <si>
+    <t>CD_M20260141109</t>
+  </si>
+  <si>
+    <t>CD_M20260141201</t>
+  </si>
+  <si>
+    <t>CD_M20260141202</t>
+  </si>
+  <si>
+    <t>CD_M20260141203</t>
+  </si>
+  <si>
+    <t>CD_M20260141204</t>
+  </si>
+  <si>
+    <t>CD_M20260141205</t>
+  </si>
+  <si>
+    <t>CD_M20260141206</t>
+  </si>
+  <si>
+    <t>CD_M20260141207</t>
+  </si>
+  <si>
+    <t>CD_M20260141301</t>
+  </si>
+  <si>
+    <t>CD_M20260141302</t>
+  </si>
+  <si>
+    <t>CD_M20260141303</t>
+  </si>
+  <si>
+    <t>CD_M20260141304</t>
+  </si>
+  <si>
+    <t>CD_M20260141305</t>
+  </si>
+  <si>
+    <t>CD_M20260141306</t>
+  </si>
+  <si>
+    <t>CD_M20260141307</t>
+  </si>
+  <si>
+    <t>CD_M20260141308</t>
+  </si>
+  <si>
+    <t>CD_M20260141401</t>
+  </si>
+  <si>
+    <t>CD_M20260141402</t>
+  </si>
+  <si>
+    <t>CD_M20260141403</t>
+  </si>
+  <si>
+    <t>CD_M20260141404</t>
+  </si>
+  <si>
+    <t>CD_M20260141405</t>
+  </si>
+  <si>
+    <t>CD_M20260141406</t>
+  </si>
+  <si>
+    <t>CD_M20260141407</t>
+  </si>
+  <si>
+    <t>CD_M20260141501</t>
+  </si>
+  <si>
+    <t>CD_M20260141502</t>
+  </si>
+  <si>
+    <t>CD_M20260141503</t>
+  </si>
+  <si>
+    <t>CD_M20260141504</t>
+  </si>
+  <si>
+    <t>CD_M20260141505</t>
+  </si>
+  <si>
+    <t>CD_M20260141506</t>
+  </si>
+  <si>
+    <t>CD_M20260141507</t>
+  </si>
+  <si>
+    <t>CD_M20260141601</t>
+  </si>
+  <si>
+    <t>CD_M20260141602</t>
+  </si>
+  <si>
+    <t>CD_M20260141603</t>
+  </si>
+  <si>
+    <t>CD_M20260141605</t>
+  </si>
+  <si>
+    <t>CD_M20260141606</t>
+  </si>
+  <si>
+    <t>CD_M20260141607</t>
+  </si>
+  <si>
+    <t>CD_M20260141604</t>
+  </si>
+  <si>
+    <t>CD_M20260141701</t>
+  </si>
+  <si>
+    <t>CD_M20260141702</t>
+  </si>
+  <si>
+    <t>CD_M20260141703</t>
+  </si>
+  <si>
+    <t>CD_M20260141704</t>
+  </si>
+  <si>
+    <t>CD_M20260141705</t>
+  </si>
+  <si>
+    <t>CD_M20260141707</t>
+  </si>
+  <si>
+    <t>CD_M20260141708</t>
+  </si>
+  <si>
+    <t>CD_M20260141706</t>
+  </si>
+  <si>
+    <t>CD_M20260141709</t>
+  </si>
+  <si>
+    <t>CD_M20260141802</t>
+  </si>
+  <si>
+    <t>CD_M20260141803</t>
+  </si>
+  <si>
+    <t>CD_M20260141804</t>
+  </si>
+  <si>
+    <t>CD_M20260141806</t>
+  </si>
+  <si>
+    <t>CD_M20260141807</t>
+  </si>
+  <si>
+    <t>CD_M20260141808</t>
+  </si>
+  <si>
+    <t>CD_M20260141809</t>
+  </si>
+  <si>
+    <t>CD_M20260141801</t>
+  </si>
+  <si>
+    <t>CD_M20260141805</t>
+  </si>
+  <si>
+    <t>CD_M20260141901</t>
+  </si>
+  <si>
+    <t>CD_M20260141902</t>
+  </si>
+  <si>
+    <t>CD_M20260141903</t>
+  </si>
+  <si>
+    <t>CD_M20260141904</t>
+  </si>
+  <si>
+    <t>CD_M20260141905</t>
+  </si>
+  <si>
+    <t>CD_M20260141907</t>
+  </si>
+  <si>
+    <t>CD_M20260141908</t>
+  </si>
+  <si>
+    <t>CD_M20260141906</t>
+  </si>
+  <si>
+    <t>CD_M20260141909</t>
+  </si>
+  <si>
+    <t>CD_M20260142002</t>
+  </si>
+  <si>
+    <t>CD_M20260142003</t>
+  </si>
+  <si>
+    <t>CD_M20260142005</t>
+  </si>
+  <si>
+    <t>CD_M20260142006</t>
+  </si>
+  <si>
+    <t>CD_M20260142007</t>
+  </si>
+  <si>
+    <t>CD_M20260142008</t>
+  </si>
+  <si>
+    <t>CD_M20260142009</t>
+  </si>
+  <si>
+    <t>CD_M20260142001</t>
+  </si>
+  <si>
+    <t>CD_M20260142004</t>
+  </si>
+  <si>
+    <t>CD_M20260142101</t>
+  </si>
+  <si>
+    <t>CD_M20260142102</t>
+  </si>
+  <si>
+    <t>CD_M20260142103</t>
+  </si>
+  <si>
+    <t>CD_M20260142105</t>
+  </si>
+  <si>
+    <t>CD_M20260142106</t>
+  </si>
+  <si>
+    <t>CD_M20260142108</t>
+  </si>
+  <si>
+    <t>CD_M20260142109</t>
+  </si>
+  <si>
+    <t>CD_M20260142107</t>
+  </si>
+  <si>
+    <t>CD_M20260142104</t>
+  </si>
+  <si>
+    <t>CD_M20260142202</t>
+  </si>
+  <si>
+    <t>CD_M20260142203</t>
+  </si>
+  <si>
+    <t>CD_M20260142204</t>
+  </si>
+  <si>
+    <t>CD_M20260142205</t>
+  </si>
+  <si>
+    <t>CD_M20260142206</t>
+  </si>
+  <si>
+    <t>CD_M20260142207</t>
+  </si>
+  <si>
+    <t>CD_M20260142209</t>
+  </si>
+  <si>
+    <t>CD_M20260142201</t>
+  </si>
+  <si>
+    <t>CD_M20260142208</t>
+  </si>
+  <si>
+    <t>CD_M20260142301</t>
+  </si>
+  <si>
+    <t>CD_M20260142302</t>
+  </si>
+  <si>
+    <t>CD_M20260142304</t>
+  </si>
+  <si>
+    <t>CD_M20260142305</t>
+  </si>
+  <si>
+    <t>CD_M20260142306</t>
+  </si>
+  <si>
+    <t>CD_M20260142308</t>
+  </si>
+  <si>
+    <t>CD_M20260142309</t>
+  </si>
+  <si>
+    <t>CD_M20260142307</t>
+  </si>
+  <si>
+    <t>CD_M20260142303</t>
+  </si>
+  <si>
+    <t>CD_M20260142402</t>
+  </si>
+  <si>
+    <t>CD_M20260142403</t>
+  </si>
+  <si>
+    <t>CD_M20260142404</t>
+  </si>
+  <si>
+    <t>CD_M20260142405</t>
+  </si>
+  <si>
+    <t>CD_M20260142406</t>
+  </si>
+  <si>
+    <t>CD_M20260142407</t>
+  </si>
+  <si>
+    <t>CD_M20260142408</t>
+  </si>
+  <si>
+    <t>CD_M20260142401</t>
+  </si>
+  <si>
+    <t>CD_M20260142409</t>
+  </si>
+  <si>
+    <t>CD_M20261010101</t>
+  </si>
+  <si>
+    <t>CD_M20261010102</t>
+  </si>
+  <si>
+    <t>CD_M20261010103</t>
+  </si>
+  <si>
+    <t>CD_M20261010104</t>
+  </si>
+  <si>
+    <t>CD_M20261010105</t>
+  </si>
+  <si>
+    <t>CD_M20261010106</t>
+  </si>
+  <si>
+    <t>CD_M20261010107</t>
+  </si>
+  <si>
+    <t>CD_M20261010108</t>
+  </si>
+  <si>
+    <t>CD_M20261010109</t>
+  </si>
+  <si>
+    <t>SEASON</t>
+  </si>
+  <si>
+    <t>1.05pm</t>
+  </si>
+  <si>
+    <t>1.35pm</t>
+  </si>
+  <si>
+    <t>Friday August 7</t>
+  </si>
+  <si>
+    <t>Friday July 10</t>
+  </si>
+  <si>
+    <t>Friday July 17</t>
+  </si>
+  <si>
+    <t>Friday July 24</t>
+  </si>
+  <si>
+    <t>Friday July 3</t>
+  </si>
+  <si>
+    <t>Friday July 31</t>
+  </si>
+  <si>
+    <t>Friday June 26</t>
+  </si>
+  <si>
+    <t>ROUND 16</t>
+  </si>
+  <si>
+    <t>ROUND 17</t>
+  </si>
+  <si>
+    <t>ROUND 18</t>
+  </si>
+  <si>
+    <t>ROUND 19</t>
+  </si>
+  <si>
+    <t>ROUND 20</t>
+  </si>
+  <si>
+    <t>ROUND 21</t>
+  </si>
+  <si>
+    <t>ROUND 22</t>
+  </si>
+  <si>
+    <t>Saturday August 1</t>
+  </si>
+  <si>
+    <t>Saturday August 8</t>
+  </si>
+  <si>
+    <t>Saturday July 11</t>
+  </si>
+  <si>
+    <t>Saturday July 18</t>
+  </si>
+  <si>
+    <t>Saturday July 25</t>
+  </si>
+  <si>
+    <t>Saturday July 4</t>
+  </si>
+  <si>
+    <t>Saturday June 27</t>
+  </si>
+  <si>
+    <t>Sunday August 2</t>
+  </si>
+  <si>
+    <t>Sunday August 9</t>
+  </si>
+  <si>
+    <t>Sunday July 12</t>
+  </si>
+  <si>
+    <t>Sunday July 19</t>
+  </si>
+  <si>
+    <t>Sunday July 26</t>
+  </si>
+  <si>
+    <t>Sunday July 5</t>
+  </si>
+  <si>
+    <t>Sunday June 28</t>
+  </si>
+  <si>
+    <t>Thursday August 6</t>
+  </si>
+  <si>
+    <t>Thursday July 16</t>
+  </si>
+  <si>
+    <t>Thursday July 2</t>
+  </si>
+  <si>
+    <t>Thursday July 23</t>
+  </si>
+  <si>
+    <t>Thursday July 30</t>
+  </si>
+  <si>
+    <t>Thursday July 9</t>
+  </si>
+  <si>
+    <t>Thursday June 25</t>
+  </si>
+  <si>
+    <t>ROUND 23</t>
+  </si>
+  <si>
+    <t>Saturday August 15</t>
+  </si>
+  <si>
+    <t>Sunday August 16</t>
+  </si>
+  <si>
+    <t>1.40pm</t>
+  </si>
+  <si>
+    <t>3.45pm</t>
+  </si>
+  <si>
+    <t>9.10pm</t>
+  </si>
+  <si>
+    <t>Friday August 14</t>
+  </si>
+  <si>
+    <t>ROUND 24</t>
+  </si>
+  <si>
+    <t>Friday August 21</t>
+  </si>
+  <si>
+    <t>Saturday August 22</t>
+  </si>
+  <si>
+    <t>Sunday August 23</t>
+  </si>
+  <si>
+    <t>12.20pm</t>
+  </si>
+  <si>
+    <t>7.45pm</t>
+  </si>
+  <si>
+    <t>Thursday August 20</t>
+  </si>
+  <si>
+    <t>3.20pm</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>

--- a/docs/assets/assets/afl_fixtures_2026.xlsx
+++ b/docs/assets/assets/afl_fixtures_2026.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD6DF45-BDF8-4AEA-9124-1E24E53366A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB1EFC8A-DC52-4305-BA12-001E6F269A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
+    <workbookView xWindow="975" yWindow="0" windowWidth="33120" windowHeight="20790" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="676">
   <si>
     <t>ROUND</t>
   </si>
@@ -926,12 +927,6 @@
     <t>https://www.afl.com.au/afl/matches/8166</t>
   </si>
   <si>
-    <t>ROUND 16 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday June 25 – Sunday June 28</t>
-  </si>
-  <si>
     <t xml:space="preserve"> The Gabba</t>
   </si>
   <si>
@@ -962,12 +957,6 @@
     <t>https://www.afl.com.au/afl/matches/8171</t>
   </si>
   <si>
-    <t>ROUND 17 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday July 2 – Sunday July 5</t>
-  </si>
-  <si>
     <t>https://www.afl.com.au/afl/matches/8173</t>
   </si>
   <si>
@@ -1007,12 +996,6 @@
     <t>https://www.afl.com.au/afl/matches/8183</t>
   </si>
   <si>
-    <t>ROUND 18 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday July 9 – Sunday July 12</t>
-  </si>
-  <si>
     <t>https://www.afl.com.au/afl/matches/8186</t>
   </si>
   <si>
@@ -1043,12 +1026,6 @@
     <t>https://www.afl.com.au/afl/matches/8189</t>
   </si>
   <si>
-    <t>ROUND 19 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday July 16 – Sunday July 19</t>
-  </si>
-  <si>
     <t>https://www.afl.com.au/afl/matches/8194</t>
   </si>
   <si>
@@ -1076,12 +1053,6 @@
     <t>https://www.afl.com.au/afl/matches/8202</t>
   </si>
   <si>
-    <t>ROUND 20 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday July 23 – Sunday July 26</t>
-  </si>
-  <si>
     <t>https://www.afl.com.au/afl/matches/8203</t>
   </si>
   <si>
@@ -1109,12 +1080,6 @@
     <t>https://www.afl.com.au/afl/matches/8210</t>
   </si>
   <si>
-    <t>ROUND 21 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday July 30 – Sunday August 2</t>
-  </si>
-  <si>
     <t>https://www.afl.com.au/afl/matches/8209</t>
   </si>
   <si>
@@ -1142,12 +1107,6 @@
     <t>https://www.afl.com.au/afl/matches/8218</t>
   </si>
   <si>
-    <t>ROUND 22 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday August 6 – Sunday August 9</t>
-  </si>
-  <si>
     <t>https://www.afl.com.au/afl/matches/8223</t>
   </si>
   <si>
@@ -1175,12 +1134,6 @@
     <t>https://www.afl.com.au/afl/matches/8227</t>
   </si>
   <si>
-    <t>ROUND 23 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday August 13 – Sunday August 16</t>
-  </si>
-  <si>
     <t>https://www.afl.com.au/afl/matches/8229</t>
   </si>
   <si>
@@ -1208,12 +1161,6 @@
     <t>https://www.afl.com.au/afl/matches/8237</t>
   </si>
   <si>
-    <t>ROUND 24 (dates and times TBC)</t>
-  </si>
-  <si>
-    <t>Thursday August 20 – Sunday August 23</t>
-  </si>
-  <si>
     <t>https://www.afl.com.au/afl/matches/8239</t>
   </si>
   <si>
@@ -2091,9 +2038,6 @@
   </si>
   <si>
     <t>3.45pm</t>
-  </si>
-  <si>
-    <t>9.10pm</t>
   </si>
   <si>
     <t>Friday August 14</t>
@@ -2518,9 +2462,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{CB6B02A0-21B2-418E-97BD-054996A22EC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB6B02A0-21B2-418E-97BD-054996A22EC7}">
   <dimension ref="A1:I217"/>
-  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
@@ -2531,9 +2475,9 @@
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ns3:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2557,18 +2501,18 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ns3:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C2" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D2" t="s">
         <v>39</v>
@@ -2577,27 +2521,27 @@
         <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="G2" t="s">
         <v>57</v>
       </c>
       <c r="H2" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="I2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ns3:dyDescent="0.25">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C3" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -2606,27 +2550,27 @@
         <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="G3" t="s">
+        <v>389</v>
+      </c>
+      <c r="H3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I3" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="s">
         <v>407</v>
       </c>
-      <c r="H3" t="s">
-        <v>408</v>
-      </c>
-      <c r="I3" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A4">
-        <v>2026</v>
-      </c>
-      <c r="B4" t="s">
-        <v>425</v>
-      </c>
       <c r="C4" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -2635,27 +2579,27 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="G4" t="s">
         <v>57</v>
       </c>
       <c r="H4" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="I4" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ns3:dyDescent="0.25">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C5" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="D5" t="s">
         <v>67</v>
@@ -2664,27 +2608,27 @@
         <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="G5" t="s">
+        <v>389</v>
+      </c>
+      <c r="H5" t="s">
+        <v>395</v>
+      </c>
+      <c r="I5" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="s">
         <v>407</v>
       </c>
-      <c r="H5" t="s">
-        <v>413</v>
-      </c>
-      <c r="I5" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A6">
-        <v>2026</v>
-      </c>
-      <c r="B6" t="s">
-        <v>425</v>
-      </c>
       <c r="C6" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="D6" t="s">
         <v>47</v>
@@ -2693,27 +2637,27 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="G6" t="s">
         <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="I6" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ns3:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C7" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="D7" t="s">
         <v>68</v>
@@ -2722,27 +2666,27 @@
         <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="G7" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="H7" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="I7" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ns3:dyDescent="0.25">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="D8" t="s">
         <v>53</v>
@@ -2751,27 +2695,27 @@
         <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="G8" t="s">
         <v>72</v>
       </c>
       <c r="H8" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="I8" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ns3:dyDescent="0.25">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2026</v>
       </c>
       <c r="B9" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C9" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D9" t="s">
         <v>63</v>
@@ -2780,27 +2724,27 @@
         <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="G9" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="H9" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="I9" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ns3:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2026</v>
       </c>
       <c r="B10" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C10" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D10" t="s">
         <v>71</v>
@@ -2809,19 +2753,19 @@
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="G10" t="s">
         <v>72</v>
       </c>
       <c r="H10" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I10" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ns3:dyDescent="0.25">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2026</v>
       </c>
@@ -2847,10 +2791,10 @@
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ns3:dyDescent="0.25">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2026</v>
       </c>
@@ -2876,10 +2820,10 @@
         <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ns3:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2026</v>
       </c>
@@ -2905,10 +2849,10 @@
         <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ns3:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2026</v>
       </c>
@@ -2934,10 +2878,10 @@
         <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ns3:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2026</v>
       </c>
@@ -2963,10 +2907,10 @@
         <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ns3:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2026</v>
       </c>
@@ -2992,10 +2936,10 @@
         <v>41</v>
       </c>
       <c r="I16" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ns3:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2026</v>
       </c>
@@ -3021,10 +2965,10 @@
         <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ns3:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -3050,10 +2994,10 @@
         <v>51</v>
       </c>
       <c r="I18" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ns3:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2026</v>
       </c>
@@ -3079,10 +3023,10 @@
         <v>55</v>
       </c>
       <c r="I19" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ns3:dyDescent="0.25">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2026</v>
       </c>
@@ -3108,10 +3052,10 @@
         <v>58</v>
       </c>
       <c r="I20" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ns3:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2026</v>
       </c>
@@ -3137,10 +3081,10 @@
         <v>61</v>
       </c>
       <c r="I21" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ns3:dyDescent="0.25">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2026</v>
       </c>
@@ -3166,10 +3110,10 @@
         <v>66</v>
       </c>
       <c r="I22" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ns3:dyDescent="0.25">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2026</v>
       </c>
@@ -3195,10 +3139,10 @@
         <v>70</v>
       </c>
       <c r="I23" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ns3:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2026</v>
       </c>
@@ -3224,10 +3168,10 @@
         <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ns3:dyDescent="0.25">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2026</v>
       </c>
@@ -3253,10 +3197,10 @@
         <v>78</v>
       </c>
       <c r="I25" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ns3:dyDescent="0.25">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2026</v>
       </c>
@@ -3282,10 +3226,10 @@
         <v>82</v>
       </c>
       <c r="I26" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ns3:dyDescent="0.25">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2026</v>
       </c>
@@ -3311,10 +3255,10 @@
         <v>86</v>
       </c>
       <c r="I27" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ns3:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2026</v>
       </c>
@@ -3340,10 +3284,10 @@
         <v>87</v>
       </c>
       <c r="I28" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ns3:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2026</v>
       </c>
@@ -3369,10 +3313,10 @@
         <v>91</v>
       </c>
       <c r="I29" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ns3:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2026</v>
       </c>
@@ -3398,10 +3342,10 @@
         <v>95</v>
       </c>
       <c r="I30" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ns3:dyDescent="0.25">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2026</v>
       </c>
@@ -3427,10 +3371,10 @@
         <v>98</v>
       </c>
       <c r="I31" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ns3:dyDescent="0.25">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2026</v>
       </c>
@@ -3456,10 +3400,10 @@
         <v>101</v>
       </c>
       <c r="I32" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ns3:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2026</v>
       </c>
@@ -3485,10 +3429,10 @@
         <v>103</v>
       </c>
       <c r="I33" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ns3:dyDescent="0.25">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2026</v>
       </c>
@@ -3514,10 +3458,10 @@
         <v>106</v>
       </c>
       <c r="I34" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ns3:dyDescent="0.25">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2026</v>
       </c>
@@ -3543,10 +3487,10 @@
         <v>107</v>
       </c>
       <c r="I35" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ns3:dyDescent="0.25">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2026</v>
       </c>
@@ -3572,10 +3516,10 @@
         <v>108</v>
       </c>
       <c r="I36" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ns3:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2026</v>
       </c>
@@ -3601,10 +3545,10 @@
         <v>111</v>
       </c>
       <c r="I37" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ns3:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2026</v>
       </c>
@@ -3630,10 +3574,10 @@
         <v>112</v>
       </c>
       <c r="I38" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ns3:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2026</v>
       </c>
@@ -3659,10 +3603,10 @@
         <v>115</v>
       </c>
       <c r="I39" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ns3:dyDescent="0.25">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2026</v>
       </c>
@@ -3688,10 +3632,10 @@
         <v>117</v>
       </c>
       <c r="I40" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ns3:dyDescent="0.25">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2026</v>
       </c>
@@ -3717,10 +3661,10 @@
         <v>119</v>
       </c>
       <c r="I41" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ns3:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2026</v>
       </c>
@@ -3746,10 +3690,10 @@
         <v>121</v>
       </c>
       <c r="I42" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ns3:dyDescent="0.25">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2026</v>
       </c>
@@ -3775,10 +3719,10 @@
         <v>122</v>
       </c>
       <c r="I43" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ns3:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2026</v>
       </c>
@@ -3804,10 +3748,10 @@
         <v>124</v>
       </c>
       <c r="I44" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ns3:dyDescent="0.25">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2026</v>
       </c>
@@ -3833,10 +3777,10 @@
         <v>125</v>
       </c>
       <c r="I45" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ns3:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2026</v>
       </c>
@@ -3862,10 +3806,10 @@
         <v>127</v>
       </c>
       <c r="I46" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ns3:dyDescent="0.25">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2026</v>
       </c>
@@ -3891,10 +3835,10 @@
         <v>130</v>
       </c>
       <c r="I47" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ns3:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2026</v>
       </c>
@@ -3920,10 +3864,10 @@
         <v>132</v>
       </c>
       <c r="I48" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ns3:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2026</v>
       </c>
@@ -3949,10 +3893,10 @@
         <v>135</v>
       </c>
       <c r="I49" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ns3:dyDescent="0.25">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2026</v>
       </c>
@@ -3978,10 +3922,10 @@
         <v>136</v>
       </c>
       <c r="I50" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ns3:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2026</v>
       </c>
@@ -4007,10 +3951,10 @@
         <v>138</v>
       </c>
       <c r="I51" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ns3:dyDescent="0.25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2026</v>
       </c>
@@ -4036,10 +3980,10 @@
         <v>139</v>
       </c>
       <c r="I52" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ns3:dyDescent="0.25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2026</v>
       </c>
@@ -4065,10 +4009,10 @@
         <v>141</v>
       </c>
       <c r="I53" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ns3:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2026</v>
       </c>
@@ -4094,10 +4038,10 @@
         <v>142</v>
       </c>
       <c r="I54" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ns3:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2026</v>
       </c>
@@ -4123,10 +4067,10 @@
         <v>143</v>
       </c>
       <c r="I55" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ns3:dyDescent="0.25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2026</v>
       </c>
@@ -4152,10 +4096,10 @@
         <v>146</v>
       </c>
       <c r="I56" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ns3:dyDescent="0.25">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2026</v>
       </c>
@@ -4181,10 +4125,10 @@
         <v>148</v>
       </c>
       <c r="I57" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ns3:dyDescent="0.25">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2026</v>
       </c>
@@ -4210,10 +4154,10 @@
         <v>150</v>
       </c>
       <c r="I58" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ns3:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2026</v>
       </c>
@@ -4239,10 +4183,10 @@
         <v>152</v>
       </c>
       <c r="I59" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ns3:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2026</v>
       </c>
@@ -4268,10 +4212,10 @@
         <v>153</v>
       </c>
       <c r="I60" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ns3:dyDescent="0.25">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2026</v>
       </c>
@@ -4297,10 +4241,10 @@
         <v>154</v>
       </c>
       <c r="I61" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ns3:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2026</v>
       </c>
@@ -4326,10 +4270,10 @@
         <v>156</v>
       </c>
       <c r="I62" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ns3:dyDescent="0.25">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2026</v>
       </c>
@@ -4355,10 +4299,10 @@
         <v>157</v>
       </c>
       <c r="I63" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ns3:dyDescent="0.25">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2026</v>
       </c>
@@ -4384,10 +4328,10 @@
         <v>159</v>
       </c>
       <c r="I64" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ns3:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2026</v>
       </c>
@@ -4413,10 +4357,10 @@
         <v>162</v>
       </c>
       <c r="I65" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ns3:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2026</v>
       </c>
@@ -4442,10 +4386,10 @@
         <v>164</v>
       </c>
       <c r="I66" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ns3:dyDescent="0.25">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2026</v>
       </c>
@@ -4471,10 +4415,10 @@
         <v>168</v>
       </c>
       <c r="I67" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ns3:dyDescent="0.25">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2026</v>
       </c>
@@ -4500,10 +4444,10 @@
         <v>169</v>
       </c>
       <c r="I68" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ns3:dyDescent="0.25">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2026</v>
       </c>
@@ -4529,10 +4473,10 @@
         <v>171</v>
       </c>
       <c r="I69" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ns3:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2026</v>
       </c>
@@ -4558,10 +4502,10 @@
         <v>173</v>
       </c>
       <c r="I70" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ns3:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2026</v>
       </c>
@@ -4587,10 +4531,10 @@
         <v>175</v>
       </c>
       <c r="I71" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ns3:dyDescent="0.25">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2026</v>
       </c>
@@ -4616,10 +4560,10 @@
         <v>176</v>
       </c>
       <c r="I72" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ns3:dyDescent="0.25">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2026</v>
       </c>
@@ -4645,10 +4589,10 @@
         <v>179</v>
       </c>
       <c r="I73" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ns3:dyDescent="0.25">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2026</v>
       </c>
@@ -4674,10 +4618,10 @@
         <v>182</v>
       </c>
       <c r="I74" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ns3:dyDescent="0.25">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2026</v>
       </c>
@@ -4703,10 +4647,10 @@
         <v>184</v>
       </c>
       <c r="I75" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ns3:dyDescent="0.25">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2026</v>
       </c>
@@ -4732,10 +4676,10 @@
         <v>186</v>
       </c>
       <c r="I76" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ns3:dyDescent="0.25">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2026</v>
       </c>
@@ -4761,10 +4705,10 @@
         <v>188</v>
       </c>
       <c r="I77" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ns3:dyDescent="0.25">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2026</v>
       </c>
@@ -4790,10 +4734,10 @@
         <v>189</v>
       </c>
       <c r="I78" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ns3:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2026</v>
       </c>
@@ -4819,10 +4763,10 @@
         <v>191</v>
       </c>
       <c r="I79" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ns3:dyDescent="0.25">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2026</v>
       </c>
@@ -4848,10 +4792,10 @@
         <v>192</v>
       </c>
       <c r="I80" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ns3:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2026</v>
       </c>
@@ -4877,10 +4821,10 @@
         <v>194</v>
       </c>
       <c r="I81" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ns3:dyDescent="0.25">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2026</v>
       </c>
@@ -4906,10 +4850,10 @@
         <v>195</v>
       </c>
       <c r="I82" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ns3:dyDescent="0.25">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2026</v>
       </c>
@@ -4935,10 +4879,10 @@
         <v>198</v>
       </c>
       <c r="I83" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ns3:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2026</v>
       </c>
@@ -4964,10 +4908,10 @@
         <v>200</v>
       </c>
       <c r="I84" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ns3:dyDescent="0.25">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2026</v>
       </c>
@@ -4993,10 +4937,10 @@
         <v>201</v>
       </c>
       <c r="I85" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ns3:dyDescent="0.25">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2026</v>
       </c>
@@ -5022,10 +4966,10 @@
         <v>203</v>
       </c>
       <c r="I86" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ns3:dyDescent="0.25">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2026</v>
       </c>
@@ -5051,10 +4995,10 @@
         <v>204</v>
       </c>
       <c r="I87" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ns3:dyDescent="0.25">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2026</v>
       </c>
@@ -5080,10 +5024,10 @@
         <v>206</v>
       </c>
       <c r="I88" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ns3:dyDescent="0.25">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2026</v>
       </c>
@@ -5109,10 +5053,10 @@
         <v>207</v>
       </c>
       <c r="I89" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ns3:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2026</v>
       </c>
@@ -5138,10 +5082,10 @@
         <v>209</v>
       </c>
       <c r="I90" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ns3:dyDescent="0.25">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2026</v>
       </c>
@@ -5167,10 +5111,10 @@
         <v>210</v>
       </c>
       <c r="I91" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ns3:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2026</v>
       </c>
@@ -5196,10 +5140,10 @@
         <v>213</v>
       </c>
       <c r="I92" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ns3:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2026</v>
       </c>
@@ -5225,10 +5169,10 @@
         <v>215</v>
       </c>
       <c r="I93" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ns3:dyDescent="0.25">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2026</v>
       </c>
@@ -5254,10 +5198,10 @@
         <v>216</v>
       </c>
       <c r="I94" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ns3:dyDescent="0.25">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2026</v>
       </c>
@@ -5283,10 +5227,10 @@
         <v>218</v>
       </c>
       <c r="I95" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ns3:dyDescent="0.25">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2026</v>
       </c>
@@ -5312,10 +5256,10 @@
         <v>219</v>
       </c>
       <c r="I96" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ns3:dyDescent="0.25">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2026</v>
       </c>
@@ -5341,10 +5285,10 @@
         <v>220</v>
       </c>
       <c r="I97" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ns3:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2026</v>
       </c>
@@ -5370,10 +5314,10 @@
         <v>222</v>
       </c>
       <c r="I98" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ns3:dyDescent="0.25">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2026</v>
       </c>
@@ -5399,10 +5343,10 @@
         <v>223</v>
       </c>
       <c r="I99" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ns3:dyDescent="0.25">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2026</v>
       </c>
@@ -5428,10 +5372,10 @@
         <v>225</v>
       </c>
       <c r="I100" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ns3:dyDescent="0.25">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2026</v>
       </c>
@@ -5457,10 +5401,10 @@
         <v>228</v>
       </c>
       <c r="I101" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ns3:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2026</v>
       </c>
@@ -5486,10 +5430,10 @@
         <v>230</v>
       </c>
       <c r="I102" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ns3:dyDescent="0.25">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2026</v>
       </c>
@@ -5515,10 +5459,10 @@
         <v>232</v>
       </c>
       <c r="I103" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ns3:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2026</v>
       </c>
@@ -5544,10 +5488,10 @@
         <v>234</v>
       </c>
       <c r="I104" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ns3:dyDescent="0.25">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2026</v>
       </c>
@@ -5573,10 +5517,10 @@
         <v>235</v>
       </c>
       <c r="I105" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ns3:dyDescent="0.25">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2026</v>
       </c>
@@ -5602,10 +5546,10 @@
         <v>236</v>
       </c>
       <c r="I106" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ns3:dyDescent="0.25">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2026</v>
       </c>
@@ -5631,10 +5575,10 @@
         <v>237</v>
       </c>
       <c r="I107" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ns3:dyDescent="0.25">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2026</v>
       </c>
@@ -5660,10 +5604,10 @@
         <v>239</v>
       </c>
       <c r="I108" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ns3:dyDescent="0.25">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2026</v>
       </c>
@@ -5689,10 +5633,10 @@
         <v>240</v>
       </c>
       <c r="I109" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ns3:dyDescent="0.25">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2026</v>
       </c>
@@ -5718,10 +5662,10 @@
         <v>243</v>
       </c>
       <c r="I110" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ns3:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2026</v>
       </c>
@@ -5747,10 +5691,10 @@
         <v>245</v>
       </c>
       <c r="I111" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ns3:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2026</v>
       </c>
@@ -5776,10 +5720,10 @@
         <v>247</v>
       </c>
       <c r="I112" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ns3:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2026</v>
       </c>
@@ -5805,10 +5749,10 @@
         <v>248</v>
       </c>
       <c r="I113" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ns3:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2026</v>
       </c>
@@ -5834,10 +5778,10 @@
         <v>249</v>
       </c>
       <c r="I114" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ns3:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2026</v>
       </c>
@@ -5863,10 +5807,10 @@
         <v>252</v>
       </c>
       <c r="I115" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ns3:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2026</v>
       </c>
@@ -5892,10 +5836,10 @@
         <v>253</v>
       </c>
       <c r="I116" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ns3:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2026</v>
       </c>
@@ -5921,10 +5865,10 @@
         <v>256</v>
       </c>
       <c r="I117" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ns3:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2026</v>
       </c>
@@ -5950,10 +5894,10 @@
         <v>258</v>
       </c>
       <c r="I118" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ns3:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2026</v>
       </c>
@@ -5979,10 +5923,10 @@
         <v>262</v>
       </c>
       <c r="I119" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ns3:dyDescent="0.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2026</v>
       </c>
@@ -6008,10 +5952,10 @@
         <v>264</v>
       </c>
       <c r="I120" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ns3:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2026</v>
       </c>
@@ -6037,10 +5981,10 @@
         <v>265</v>
       </c>
       <c r="I121" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ns3:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2026</v>
       </c>
@@ -6066,10 +6010,10 @@
         <v>267</v>
       </c>
       <c r="I122" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ns3:dyDescent="0.25">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2026</v>
       </c>
@@ -6095,10 +6039,10 @@
         <v>268</v>
       </c>
       <c r="I123" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ns3:dyDescent="0.25">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2026</v>
       </c>
@@ -6124,10 +6068,10 @@
         <v>270</v>
       </c>
       <c r="I124" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ns3:dyDescent="0.25">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2026</v>
       </c>
@@ -6153,10 +6097,10 @@
         <v>273</v>
       </c>
       <c r="I125" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ns3:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2026</v>
       </c>
@@ -6182,10 +6126,10 @@
         <v>275</v>
       </c>
       <c r="I126" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ns3:dyDescent="0.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2026</v>
       </c>
@@ -6211,10 +6155,10 @@
         <v>277</v>
       </c>
       <c r="I127" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ns3:dyDescent="0.25">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2026</v>
       </c>
@@ -6240,10 +6184,10 @@
         <v>278</v>
       </c>
       <c r="I128" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ns3:dyDescent="0.25">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2026</v>
       </c>
@@ -6269,10 +6213,10 @@
         <v>279</v>
       </c>
       <c r="I129" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ns3:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2026</v>
       </c>
@@ -6298,10 +6242,10 @@
         <v>282</v>
       </c>
       <c r="I130" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ns3:dyDescent="0.25">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2026</v>
       </c>
@@ -6327,10 +6271,10 @@
         <v>283</v>
       </c>
       <c r="I131" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ns3:dyDescent="0.25">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2026</v>
       </c>
@@ -6356,10 +6300,10 @@
         <v>286</v>
       </c>
       <c r="I132" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ns3:dyDescent="0.25">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2026</v>
       </c>
@@ -6385,10 +6329,10 @@
         <v>288</v>
       </c>
       <c r="I133" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ns3:dyDescent="0.25">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2026</v>
       </c>
@@ -6414,10 +6358,10 @@
         <v>290</v>
       </c>
       <c r="I134" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ns3:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2026</v>
       </c>
@@ -6443,10 +6387,10 @@
         <v>291</v>
       </c>
       <c r="I135" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ns3:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2026</v>
       </c>
@@ -6472,10 +6416,10 @@
         <v>292</v>
       </c>
       <c r="I136" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ns3:dyDescent="0.25">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2026</v>
       </c>
@@ -6501,10 +6445,10 @@
         <v>294</v>
       </c>
       <c r="I137" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ns3:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2026</v>
       </c>
@@ -6530,18 +6474,18 @@
         <v>295</v>
       </c>
       <c r="I138" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" ns3:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2026</v>
       </c>
       <c r="B139" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C139" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="D139" t="s">
         <v>26</v>
@@ -6550,27 +6494,27 @@
         <v>77</v>
       </c>
       <c r="F139" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G139" t="s">
         <v>12</v>
       </c>
       <c r="H139" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I139" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ns3:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2026</v>
       </c>
       <c r="B140" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C140" t="s">
-        <v>651</v>
+        <v>633</v>
       </c>
       <c r="D140" t="s">
         <v>76</v>
@@ -6579,27 +6523,27 @@
         <v>48</v>
       </c>
       <c r="F140" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G140" t="s">
         <v>44</v>
       </c>
       <c r="H140" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I140" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" ns3:dyDescent="0.25">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2026</v>
       </c>
       <c r="B141" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C141" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="D141" t="s">
         <v>39</v>
@@ -6614,21 +6558,21 @@
         <v>50</v>
       </c>
       <c r="H141" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I141" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" ns3:dyDescent="0.25">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2026</v>
       </c>
       <c r="B142" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C142" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="D142" t="s">
         <v>59</v>
@@ -6637,27 +6581,27 @@
         <v>40</v>
       </c>
       <c r="F142" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G142" t="s">
         <v>24</v>
       </c>
       <c r="H142" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I142" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ns3:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2026</v>
       </c>
       <c r="B143" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C143" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="D143" t="s">
         <v>93</v>
@@ -6672,21 +6616,21 @@
         <v>29</v>
       </c>
       <c r="H143" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I143" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" ns3:dyDescent="0.25">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2026</v>
       </c>
       <c r="B144" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C144" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="D144" t="s">
         <v>63</v>
@@ -6701,21 +6645,21 @@
         <v>69</v>
       </c>
       <c r="H144" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I144" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" ns3:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2026</v>
       </c>
       <c r="B145" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C145" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="D145" t="s">
         <v>88</v>
@@ -6724,27 +6668,27 @@
         <v>85</v>
       </c>
       <c r="F145" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G145" t="s">
         <v>158</v>
       </c>
       <c r="H145" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I145" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ns3:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2026</v>
       </c>
       <c r="B146" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C146" t="s">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="D146" t="s">
         <v>52</v>
@@ -6753,27 +6697,27 @@
         <v>56</v>
       </c>
       <c r="F146" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G146" t="s">
         <v>12</v>
       </c>
       <c r="H146" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I146" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ns3:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2026</v>
       </c>
       <c r="B147" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C147" t="s">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="D147" t="s">
         <v>9</v>
@@ -6782,27 +6726,27 @@
         <v>27</v>
       </c>
       <c r="F147" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G147" t="s">
         <v>44</v>
       </c>
       <c r="H147" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I147" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" ns3:dyDescent="0.25">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2026</v>
       </c>
       <c r="B148" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C148" t="s">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="D148" t="s">
         <v>96</v>
@@ -6811,27 +6755,27 @@
         <v>60</v>
       </c>
       <c r="F148" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G148" t="s">
         <v>185</v>
       </c>
       <c r="H148" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I148" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" ns3:dyDescent="0.25">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2026</v>
       </c>
       <c r="B149" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C149" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="D149" t="s">
         <v>76</v>
@@ -6840,27 +6784,27 @@
         <v>89</v>
       </c>
       <c r="F149" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G149" t="s">
         <v>50</v>
       </c>
       <c r="H149" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I149" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" ns3:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2026</v>
       </c>
       <c r="B150" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C150" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="D150" t="s">
         <v>21</v>
@@ -6872,24 +6816,24 @@
         <v>177</v>
       </c>
       <c r="G150" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="H150" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I150" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" ns3:dyDescent="0.25">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2026</v>
       </c>
       <c r="B151" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C151" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="D151" t="s">
         <v>15</v>
@@ -6898,27 +6842,27 @@
         <v>33</v>
       </c>
       <c r="F151" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G151" t="s">
         <v>24</v>
       </c>
       <c r="H151" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I151" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ns3:dyDescent="0.25">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2026</v>
       </c>
       <c r="B152" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C152" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="D152" t="s">
         <v>84</v>
@@ -6927,27 +6871,27 @@
         <v>10</v>
       </c>
       <c r="F152" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G152" t="s">
         <v>29</v>
       </c>
       <c r="H152" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I152" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" ns3:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2026</v>
       </c>
       <c r="B153" t="s">
+        <v>635</v>
+      </c>
+      <c r="C153" t="s">
         <v>653</v>
-      </c>
-      <c r="C153" t="s">
-        <v>671</v>
       </c>
       <c r="D153" t="s">
         <v>43</v>
@@ -6962,21 +6906,21 @@
         <v>69</v>
       </c>
       <c r="H153" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I153" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" ns3:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2026</v>
       </c>
       <c r="B154" t="s">
+        <v>635</v>
+      </c>
+      <c r="C154" t="s">
         <v>653</v>
-      </c>
-      <c r="C154" t="s">
-        <v>671</v>
       </c>
       <c r="D154" t="s">
         <v>93</v>
@@ -6991,21 +6935,21 @@
         <v>178</v>
       </c>
       <c r="H154" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I154" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" ns3:dyDescent="0.25">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2026</v>
       </c>
       <c r="B155" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C155" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="D155" t="s">
         <v>88</v>
@@ -7014,27 +6958,27 @@
         <v>77</v>
       </c>
       <c r="F155" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G155" t="s">
         <v>185</v>
       </c>
       <c r="H155" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I155" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" ns3:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2026</v>
       </c>
       <c r="B156" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C156" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="D156" t="s">
         <v>59</v>
@@ -7049,21 +6993,21 @@
         <v>44</v>
       </c>
       <c r="H156" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="I156" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ns3:dyDescent="0.25">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2026</v>
       </c>
       <c r="B157" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C157" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="D157" t="s">
         <v>32</v>
@@ -7078,21 +7022,21 @@
         <v>50</v>
       </c>
       <c r="H157" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="I157" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ns3:dyDescent="0.25">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2026</v>
       </c>
       <c r="B158" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C158" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="D158" t="s">
         <v>21</v>
@@ -7101,27 +7045,27 @@
         <v>16</v>
       </c>
       <c r="F158" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="G158" t="s">
         <v>24</v>
       </c>
       <c r="H158" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I158" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" ns3:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2026</v>
       </c>
       <c r="B159" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C159" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="D159" t="s">
         <v>39</v>
@@ -7130,27 +7074,27 @@
         <v>22</v>
       </c>
       <c r="F159" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G159" t="s">
         <v>29</v>
       </c>
       <c r="H159" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="I159" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" ns3:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2026</v>
       </c>
       <c r="B160" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C160" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="D160" t="s">
         <v>80</v>
@@ -7165,21 +7109,21 @@
         <v>185</v>
       </c>
       <c r="H160" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I160" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ns3:dyDescent="0.25">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2026</v>
       </c>
       <c r="B161" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C161" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="D161" t="s">
         <v>47</v>
@@ -7194,21 +7138,21 @@
         <v>65</v>
       </c>
       <c r="H161" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I161" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" ns3:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2026</v>
       </c>
       <c r="B162" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C162" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="D162" t="s">
         <v>67</v>
@@ -7217,27 +7161,27 @@
         <v>40</v>
       </c>
       <c r="F162" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G162" t="s">
         <v>69</v>
       </c>
       <c r="H162" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="I162" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ns3:dyDescent="0.25">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2026</v>
       </c>
       <c r="B163" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C163" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="D163" t="s">
         <v>26</v>
@@ -7246,27 +7190,27 @@
         <v>94</v>
       </c>
       <c r="F163" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G163" t="s">
         <v>178</v>
       </c>
       <c r="H163" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I163" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" ns3:dyDescent="0.25">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2026</v>
       </c>
       <c r="B164" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C164" t="s">
-        <v>674</v>
+        <v>656</v>
       </c>
       <c r="D164" t="s">
         <v>52</v>
@@ -7275,27 +7219,27 @@
         <v>68</v>
       </c>
       <c r="F164" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G164" t="s">
         <v>12</v>
       </c>
       <c r="H164" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="I164" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" ns3:dyDescent="0.25">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2026</v>
       </c>
       <c r="B165" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C165" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -7304,27 +7248,27 @@
         <v>60</v>
       </c>
       <c r="F165" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G165" t="s">
         <v>44</v>
       </c>
       <c r="H165" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="I165" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" ns3:dyDescent="0.25">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2026</v>
       </c>
       <c r="B166" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C166" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="D166" t="s">
         <v>93</v>
@@ -7339,21 +7283,21 @@
         <v>50</v>
       </c>
       <c r="H166" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="I166" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" ns3:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2026</v>
       </c>
       <c r="B167" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C167" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="D167" t="s">
         <v>63</v>
@@ -7368,21 +7312,21 @@
         <v>24</v>
       </c>
       <c r="H167" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I167" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" ns3:dyDescent="0.25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2026</v>
       </c>
       <c r="B168" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C168" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="D168" t="s">
         <v>59</v>
@@ -7391,27 +7335,27 @@
         <v>10</v>
       </c>
       <c r="F168" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G168" t="s">
         <v>29</v>
       </c>
       <c r="H168" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I168" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" ns3:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2026</v>
       </c>
       <c r="B169" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C169" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="D169" t="s">
         <v>96</v>
@@ -7420,27 +7364,27 @@
         <v>56</v>
       </c>
       <c r="F169" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G169" t="s">
         <v>185</v>
       </c>
       <c r="H169" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="I169" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" ns3:dyDescent="0.25">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2026</v>
       </c>
       <c r="B170" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C170" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="D170" t="s">
         <v>84</v>
@@ -7449,27 +7393,27 @@
         <v>22</v>
       </c>
       <c r="F170" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G170" t="s">
         <v>65</v>
       </c>
       <c r="H170" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I170" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" ns3:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2026</v>
       </c>
       <c r="B171" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C171" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="D171" t="s">
         <v>15</v>
@@ -7478,27 +7422,27 @@
         <v>27</v>
       </c>
       <c r="F171" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G171" t="s">
         <v>69</v>
       </c>
       <c r="H171" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I171" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" ns3:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2026</v>
       </c>
       <c r="B172" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C172" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="D172" t="s">
         <v>43</v>
@@ -7513,21 +7457,21 @@
         <v>178</v>
       </c>
       <c r="H172" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I172" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" ns3:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2026</v>
       </c>
       <c r="B173" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C173" t="s">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="D173" t="s">
         <v>80</v>
@@ -7542,21 +7486,21 @@
         <v>12</v>
       </c>
       <c r="H173" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="I173" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" ns3:dyDescent="0.25">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2026</v>
       </c>
       <c r="B174" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C174" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="D174" t="s">
         <v>67</v>
@@ -7565,27 +7509,27 @@
         <v>16</v>
       </c>
       <c r="F174" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G174" t="s">
         <v>44</v>
       </c>
       <c r="H174" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="I174" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" ns3:dyDescent="0.25">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2026</v>
       </c>
       <c r="B175" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C175" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="D175" t="s">
         <v>88</v>
@@ -7594,27 +7538,27 @@
         <v>71</v>
       </c>
       <c r="F175" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G175" t="s">
         <v>185</v>
       </c>
       <c r="H175" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I175" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" ns3:dyDescent="0.25">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2026</v>
       </c>
       <c r="B176" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C176" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="D176" t="s">
         <v>39</v>
@@ -7626,24 +7570,24 @@
         <v>49</v>
       </c>
       <c r="G176" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="H176" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I176" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" ns3:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2026</v>
       </c>
       <c r="B177" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C177" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="D177" t="s">
         <v>76</v>
@@ -7652,27 +7596,27 @@
         <v>94</v>
       </c>
       <c r="F177" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G177" t="s">
         <v>24</v>
       </c>
       <c r="H177" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="I177" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" ns3:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2026</v>
       </c>
       <c r="B178" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C178" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="D178" t="s">
         <v>21</v>
@@ -7681,27 +7625,27 @@
         <v>77</v>
       </c>
       <c r="F178" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="G178" t="s">
         <v>190</v>
       </c>
       <c r="H178" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="I178" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" ns3:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2026</v>
       </c>
       <c r="B179" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C179" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="D179" t="s">
         <v>47</v>
@@ -7716,21 +7660,21 @@
         <v>44</v>
       </c>
       <c r="H179" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="I179" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" ns3:dyDescent="0.25">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2026</v>
       </c>
       <c r="B180" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C180" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="D180" t="s">
         <v>26</v>
@@ -7739,27 +7683,27 @@
         <v>64</v>
       </c>
       <c r="F180" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G180" t="s">
         <v>65</v>
       </c>
       <c r="H180" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I180" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" ns3:dyDescent="0.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2026</v>
       </c>
       <c r="B181" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="C181" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="D181" t="s">
         <v>63</v>
@@ -7774,21 +7718,21 @@
         <v>69</v>
       </c>
       <c r="H181" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="I181" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" ns3:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2026</v>
       </c>
       <c r="B182" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C182" t="s">
-        <v>677</v>
+        <v>659</v>
       </c>
       <c r="D182" t="s">
         <v>59</v>
@@ -7797,27 +7741,27 @@
         <v>16</v>
       </c>
       <c r="F182" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G182" t="s">
         <v>12</v>
       </c>
       <c r="H182" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="I182" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" ns3:dyDescent="0.25">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2026</v>
       </c>
       <c r="B183" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C183" t="s">
-        <v>650</v>
+        <v>632</v>
       </c>
       <c r="D183" t="s">
         <v>88</v>
@@ -7826,27 +7770,27 @@
         <v>27</v>
       </c>
       <c r="F183" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G183" t="s">
         <v>185</v>
       </c>
       <c r="H183" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="I183" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" ns3:dyDescent="0.25">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2026</v>
       </c>
       <c r="B184" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C184" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="D184" t="s">
         <v>32</v>
@@ -7858,24 +7802,24 @@
         <v>49</v>
       </c>
       <c r="G184" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="H184" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="I184" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" ns3:dyDescent="0.25">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2026</v>
       </c>
       <c r="B185" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C185" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="D185" t="s">
         <v>76</v>
@@ -7884,27 +7828,27 @@
         <v>97</v>
       </c>
       <c r="F185" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G185" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="H185" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="I185" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" ns3:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2026</v>
       </c>
       <c r="B186" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C186" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="D186" t="s">
         <v>93</v>
@@ -7919,21 +7863,21 @@
         <v>170</v>
       </c>
       <c r="H186" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="I186" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" ns3:dyDescent="0.25">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2026</v>
       </c>
       <c r="B187" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C187" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="D187" t="s">
         <v>39</v>
@@ -7948,21 +7892,21 @@
         <v>44</v>
       </c>
       <c r="H187" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="I187" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" ns3:dyDescent="0.25">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2026</v>
       </c>
       <c r="B188" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C188" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="D188" t="s">
         <v>84</v>
@@ -7971,27 +7915,27 @@
         <v>71</v>
       </c>
       <c r="F188" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G188" t="s">
         <v>65</v>
       </c>
       <c r="H188" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="I188" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" ns3:dyDescent="0.25">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2026</v>
       </c>
       <c r="B189" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C189" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="D189" t="s">
         <v>15</v>
@@ -8000,27 +7944,27 @@
         <v>89</v>
       </c>
       <c r="F189" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G189" t="s">
         <v>69</v>
       </c>
       <c r="H189" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="I189" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" ns3:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2026</v>
       </c>
       <c r="B190" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C190" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="D190" t="s">
         <v>43</v>
@@ -8035,21 +7979,21 @@
         <v>178</v>
       </c>
       <c r="H190" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="I190" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" ns3:dyDescent="0.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2026</v>
       </c>
       <c r="B191" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C191" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="D191" t="s">
         <v>47</v>
@@ -8064,21 +8008,21 @@
         <v>12</v>
       </c>
       <c r="H191" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="I191" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" ns3:dyDescent="0.25">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2026</v>
       </c>
       <c r="B192" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C192" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="D192" t="s">
         <v>26</v>
@@ -8087,27 +8031,27 @@
         <v>22</v>
       </c>
       <c r="F192" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G192" t="s">
         <v>44</v>
       </c>
       <c r="H192" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="I192" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" ns3:dyDescent="0.25">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2026</v>
       </c>
       <c r="B193" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C193" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="D193" t="s">
         <v>67</v>
@@ -8116,27 +8060,27 @@
         <v>53</v>
       </c>
       <c r="F193" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G193" t="s">
         <v>50</v>
       </c>
       <c r="H193" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="I193" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" ns3:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2026</v>
       </c>
       <c r="B194" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C194" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="D194" t="s">
         <v>9</v>
@@ -8145,27 +8089,27 @@
         <v>64</v>
       </c>
       <c r="F194" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G194" t="s">
         <v>24</v>
       </c>
       <c r="H194" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="I194" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" ns3:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2026</v>
       </c>
       <c r="B195" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C195" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="D195" t="s">
         <v>52</v>
@@ -8174,27 +8118,27 @@
         <v>94</v>
       </c>
       <c r="F195" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G195" t="s">
         <v>190</v>
       </c>
       <c r="H195" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="I195" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" ns3:dyDescent="0.25">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2026</v>
       </c>
       <c r="B196" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C196" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="D196" t="s">
         <v>80</v>
@@ -8209,21 +8153,21 @@
         <v>29</v>
       </c>
       <c r="H196" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="I196" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" ns3:dyDescent="0.25">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2026</v>
       </c>
       <c r="B197" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C197" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="D197" t="s">
         <v>21</v>
@@ -8238,21 +8182,21 @@
         <v>65</v>
       </c>
       <c r="H197" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="I197" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" ns3:dyDescent="0.25">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2026</v>
       </c>
       <c r="B198" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C198" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="D198" t="s">
         <v>96</v>
@@ -8261,27 +8205,27 @@
         <v>33</v>
       </c>
       <c r="F198" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G198" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="H198" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="I198" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" ns3:dyDescent="0.25">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2026</v>
       </c>
       <c r="B199" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C199" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="D199" t="s">
         <v>32</v>
@@ -8296,514 +8240,514 @@
         <v>35</v>
       </c>
       <c r="H199" t="s">
+        <v>360</v>
+      </c>
+      <c r="I199" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="s">
+        <v>662</v>
+      </c>
+      <c r="C200" t="s">
+        <v>667</v>
+      </c>
+      <c r="D200" t="s">
+        <v>88</v>
+      </c>
+      <c r="E200" t="s">
+        <v>60</v>
+      </c>
+      <c r="F200" t="s">
+        <v>304</v>
+      </c>
+      <c r="G200" t="s">
+        <v>185</v>
+      </c>
+      <c r="H200" t="s">
+        <v>373</v>
+      </c>
+      <c r="I200" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="s">
+        <v>662</v>
+      </c>
+      <c r="C201" t="s">
+        <v>663</v>
+      </c>
+      <c r="D201" t="s">
+        <v>84</v>
+      </c>
+      <c r="E201" t="s">
+        <v>68</v>
+      </c>
+      <c r="F201" t="s">
+        <v>299</v>
+      </c>
+      <c r="G201" t="s">
+        <v>105</v>
+      </c>
+      <c r="H201" t="s">
+        <v>370</v>
+      </c>
+      <c r="I201" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="s">
+        <v>662</v>
+      </c>
+      <c r="C202" t="s">
+        <v>663</v>
+      </c>
+      <c r="D202" t="s">
+        <v>63</v>
+      </c>
+      <c r="E202" t="s">
+        <v>16</v>
+      </c>
+      <c r="F202" t="s">
+        <v>49</v>
+      </c>
+      <c r="G202" t="s">
+        <v>666</v>
+      </c>
+      <c r="H202" t="s">
+        <v>369</v>
+      </c>
+      <c r="I202" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>2026</v>
+      </c>
+      <c r="B203" t="s">
+        <v>662</v>
+      </c>
+      <c r="C203" t="s">
+        <v>663</v>
+      </c>
+      <c r="D203" t="s">
+        <v>26</v>
+      </c>
+      <c r="E203" t="s">
+        <v>85</v>
+      </c>
+      <c r="F203" t="s">
+        <v>296</v>
+      </c>
+      <c r="G203" t="s">
+        <v>24</v>
+      </c>
+      <c r="H203" t="s">
+        <v>365</v>
+      </c>
+      <c r="I203" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>2026</v>
+      </c>
+      <c r="B204" t="s">
+        <v>662</v>
+      </c>
+      <c r="C204" t="s">
+        <v>663</v>
+      </c>
+      <c r="D204" t="s">
+        <v>76</v>
+      </c>
+      <c r="E204" t="s">
+        <v>33</v>
+      </c>
+      <c r="F204" t="s">
+        <v>299</v>
+      </c>
+      <c r="G204" t="s">
+        <v>44</v>
+      </c>
+      <c r="H204" t="s">
+        <v>368</v>
+      </c>
+      <c r="I204" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>2026</v>
+      </c>
+      <c r="B205" t="s">
+        <v>662</v>
+      </c>
+      <c r="C205" t="s">
+        <v>663</v>
+      </c>
+      <c r="D205" t="s">
+        <v>93</v>
+      </c>
+      <c r="E205" t="s">
+        <v>89</v>
+      </c>
+      <c r="F205" t="s">
+        <v>81</v>
+      </c>
+      <c r="G205" t="s">
+        <v>185</v>
+      </c>
+      <c r="H205" t="s">
+        <v>372</v>
+      </c>
+      <c r="I205" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>2026</v>
+      </c>
+      <c r="B206" t="s">
+        <v>662</v>
+      </c>
+      <c r="C206" t="s">
+        <v>664</v>
+      </c>
+      <c r="D206" t="s">
+        <v>21</v>
+      </c>
+      <c r="E206" t="s">
+        <v>71</v>
+      </c>
+      <c r="F206" t="s">
+        <v>322</v>
+      </c>
+      <c r="G206" t="s">
+        <v>665</v>
+      </c>
+      <c r="H206" t="s">
+        <v>367</v>
+      </c>
+      <c r="I206" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>2026</v>
+      </c>
+      <c r="B207" t="s">
+        <v>662</v>
+      </c>
+      <c r="C207" t="s">
+        <v>664</v>
+      </c>
+      <c r="D207" t="s">
+        <v>47</v>
+      </c>
+      <c r="E207" t="s">
+        <v>10</v>
+      </c>
+      <c r="F207" t="s">
+        <v>49</v>
+      </c>
+      <c r="G207" t="s">
+        <v>69</v>
+      </c>
+      <c r="H207" t="s">
+        <v>371</v>
+      </c>
+      <c r="I207" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>2026</v>
+      </c>
+      <c r="B208" t="s">
+        <v>662</v>
+      </c>
+      <c r="C208" t="s">
+        <v>664</v>
+      </c>
+      <c r="D208" t="s">
+        <v>43</v>
+      </c>
+      <c r="E208" t="s">
+        <v>77</v>
+      </c>
+      <c r="F208" t="s">
+        <v>299</v>
+      </c>
+      <c r="G208" t="s">
+        <v>178</v>
+      </c>
+      <c r="H208" t="s">
+        <v>366</v>
+      </c>
+      <c r="I208" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>2026</v>
+      </c>
+      <c r="B209" t="s">
+        <v>668</v>
+      </c>
+      <c r="C209" t="s">
+        <v>674</v>
+      </c>
+      <c r="D209" t="s">
+        <v>32</v>
+      </c>
+      <c r="E209" t="s">
+        <v>85</v>
+      </c>
+      <c r="F209" t="s">
+        <v>49</v>
+      </c>
+      <c r="G209" t="s">
+        <v>12</v>
+      </c>
+      <c r="H209" t="s">
+        <v>379</v>
+      </c>
+      <c r="I209" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>2026</v>
+      </c>
+      <c r="B210" t="s">
+        <v>668</v>
+      </c>
+      <c r="C210" t="s">
+        <v>669</v>
+      </c>
+      <c r="D210" t="s">
+        <v>59</v>
+      </c>
+      <c r="E210" t="s">
+        <v>56</v>
+      </c>
+      <c r="F210" t="s">
+        <v>299</v>
+      </c>
+      <c r="G210" t="s">
+        <v>44</v>
+      </c>
+      <c r="H210" t="s">
         <v>374</v>
       </c>
-      <c r="I199" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A200">
-        <v>2026</v>
-      </c>
-      <c r="B200" t="s">
-        <v>680</v>
-      </c>
-      <c r="C200" t="s">
-        <v>681</v>
-      </c>
-      <c r="D200" t="s">
-        <v>26</v>
-      </c>
-      <c r="E200" t="s">
-        <v>85</v>
-      </c>
-      <c r="F200" t="s">
-        <v>298</v>
-      </c>
-      <c r="H200" t="s">
-        <v>381</v>
-      </c>
-      <c r="I200" t="s">
-        <v>615</v>
-      </c>
-      <c r="G200" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A201">
-        <v>2026</v>
-      </c>
-      <c r="B201" t="s">
-        <v>680</v>
-      </c>
-      <c r="C201" t="s">
-        <v>682</v>
-      </c>
-      <c r="D201" t="s">
-        <v>43</v>
-      </c>
-      <c r="E201" t="s">
-        <v>77</v>
-      </c>
-      <c r="F201" t="s">
-        <v>301</v>
-      </c>
-      <c r="H201" t="s">
-        <v>382</v>
-      </c>
-      <c r="I201" t="s">
-        <v>616</v>
-      </c>
-      <c r="G201" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A202">
-        <v>2026</v>
-      </c>
-      <c r="B202" t="s">
-        <v>680</v>
-      </c>
-      <c r="C202" t="s">
-        <v>682</v>
-      </c>
-      <c r="D202" t="s">
-        <v>21</v>
-      </c>
-      <c r="E202" t="s">
-        <v>71</v>
-      </c>
-      <c r="F202" t="s">
-        <v>328</v>
-      </c>
-      <c r="H202" t="s">
-        <v>383</v>
-      </c>
-      <c r="I202" t="s">
-        <v>617</v>
-      </c>
-      <c r="G202" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A203">
-        <v>2026</v>
-      </c>
-      <c r="B203" t="s">
-        <v>680</v>
-      </c>
-      <c r="C203" t="s">
-        <v>681</v>
-      </c>
-      <c r="D203" t="s">
-        <v>76</v>
-      </c>
-      <c r="E203" t="s">
-        <v>33</v>
-      </c>
-      <c r="F203" t="s">
-        <v>301</v>
-      </c>
-      <c r="H203" t="s">
-        <v>384</v>
-      </c>
-      <c r="I203" t="s">
-        <v>618</v>
-      </c>
-      <c r="G203" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A204">
-        <v>2026</v>
-      </c>
-      <c r="B204" t="s">
-        <v>680</v>
-      </c>
-      <c r="C204" t="s">
-        <v>681</v>
-      </c>
-      <c r="D204" t="s">
-        <v>63</v>
-      </c>
-      <c r="E204" t="s">
-        <v>16</v>
-      </c>
-      <c r="F204" t="s">
-        <v>49</v>
-      </c>
-      <c r="H204" t="s">
-        <v>385</v>
-      </c>
-      <c r="I204" t="s">
-        <v>619</v>
-      </c>
-      <c r="G204" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A205">
-        <v>2026</v>
-      </c>
-      <c r="B205" t="s">
-        <v>680</v>
-      </c>
-      <c r="C205" t="s">
-        <v>681</v>
-      </c>
-      <c r="D205" t="s">
-        <v>84</v>
-      </c>
-      <c r="E205" t="s">
-        <v>68</v>
-      </c>
-      <c r="F205" t="s">
-        <v>301</v>
-      </c>
-      <c r="H205" t="s">
-        <v>386</v>
-      </c>
-      <c r="I205" t="s">
-        <v>620</v>
-      </c>
-      <c r="G205" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A206">
-        <v>2026</v>
-      </c>
-      <c r="B206" t="s">
-        <v>680</v>
-      </c>
-      <c r="C206" t="s">
-        <v>682</v>
-      </c>
-      <c r="D206" t="s">
-        <v>47</v>
-      </c>
-      <c r="E206" t="s">
-        <v>10</v>
-      </c>
-      <c r="F206" t="s">
-        <v>49</v>
-      </c>
-      <c r="H206" t="s">
-        <v>387</v>
-      </c>
-      <c r="I206" t="s">
-        <v>621</v>
-      </c>
-      <c r="G206" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A207">
-        <v>2026</v>
-      </c>
-      <c r="B207" t="s">
-        <v>680</v>
-      </c>
-      <c r="C207" t="s">
-        <v>681</v>
-      </c>
-      <c r="D207" t="s">
-        <v>93</v>
-      </c>
-      <c r="E207" t="s">
-        <v>89</v>
-      </c>
-      <c r="F207" t="s">
-        <v>81</v>
-      </c>
-      <c r="H207" t="s">
-        <v>388</v>
-      </c>
-      <c r="I207" t="s">
-        <v>622</v>
-      </c>
-      <c r="G207" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A208">
-        <v>2026</v>
-      </c>
-      <c r="B208" t="s">
-        <v>680</v>
-      </c>
-      <c r="C208" t="s">
-        <v>686</v>
-      </c>
-      <c r="D208" t="s">
-        <v>88</v>
-      </c>
-      <c r="E208" t="s">
-        <v>60</v>
-      </c>
-      <c r="F208" t="s">
-        <v>306</v>
-      </c>
-      <c r="H208" t="s">
-        <v>389</v>
-      </c>
-      <c r="I208" t="s">
-        <v>623</v>
-      </c>
-      <c r="G208" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A209">
-        <v>2026</v>
-      </c>
-      <c r="B209" t="s">
-        <v>687</v>
-      </c>
-      <c r="C209" t="s">
-        <v>688</v>
-      </c>
-      <c r="D209" t="s">
-        <v>59</v>
-      </c>
-      <c r="E209" t="s">
-        <v>56</v>
-      </c>
-      <c r="F209" t="s">
-        <v>301</v>
-      </c>
-      <c r="H209" t="s">
-        <v>392</v>
-      </c>
-      <c r="I209" t="s">
-        <v>624</v>
-      </c>
-      <c r="G209" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A210">
-        <v>2026</v>
-      </c>
-      <c r="B210" t="s">
-        <v>687</v>
-      </c>
-      <c r="C210" t="s">
-        <v>689</v>
-      </c>
-      <c r="D210" t="s">
+      <c r="I210" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>2026</v>
+      </c>
+      <c r="B211" t="s">
+        <v>668</v>
+      </c>
+      <c r="C211" t="s">
+        <v>670</v>
+      </c>
+      <c r="D211" t="s">
         <v>39</v>
       </c>
-      <c r="E210" t="s">
+      <c r="E211" t="s">
         <v>53</v>
-      </c>
-      <c r="F210" t="s">
-        <v>49</v>
-      </c>
-      <c r="H210" t="s">
-        <v>393</v>
-      </c>
-      <c r="I210" t="s">
-        <v>625</v>
-      </c>
-      <c r="G210" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A211">
-        <v>2026</v>
-      </c>
-      <c r="B211" t="s">
-        <v>687</v>
-      </c>
-      <c r="C211" t="s">
-        <v>690</v>
-      </c>
-      <c r="D211" t="s">
-        <v>43</v>
-      </c>
-      <c r="E211" t="s">
-        <v>64</v>
       </c>
       <c r="F211" t="s">
         <v>49</v>
       </c>
+      <c r="G211" t="s">
+        <v>50</v>
+      </c>
       <c r="H211" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="I211" t="s">
-        <v>626</v>
-      </c>
-      <c r="G211" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" ns3:dyDescent="0.25">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2026</v>
       </c>
       <c r="B212" t="s">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="C212" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="D212" t="s">
+        <v>67</v>
+      </c>
+      <c r="E212" t="s">
+        <v>27</v>
+      </c>
+      <c r="F212" t="s">
+        <v>299</v>
+      </c>
+      <c r="G212" t="s">
+        <v>24</v>
+      </c>
+      <c r="H212" t="s">
+        <v>378</v>
+      </c>
+      <c r="I212" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>2026</v>
+      </c>
+      <c r="B213" t="s">
+        <v>668</v>
+      </c>
+      <c r="C213" t="s">
+        <v>670</v>
+      </c>
+      <c r="D213" t="s">
         <v>52</v>
       </c>
-      <c r="E212" t="s">
+      <c r="E213" t="s">
         <v>40</v>
       </c>
-      <c r="F212" t="s">
-        <v>311</v>
-      </c>
-      <c r="H212" t="s">
-        <v>395</v>
-      </c>
-      <c r="I212" t="s">
-        <v>627</v>
-      </c>
-      <c r="G212" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A213">
-        <v>2026</v>
-      </c>
-      <c r="B213" t="s">
-        <v>687</v>
-      </c>
-      <c r="C213" t="s">
-        <v>689</v>
-      </c>
-      <c r="D213" t="s">
-        <v>67</v>
-      </c>
-      <c r="E213" t="s">
-        <v>27</v>
-      </c>
       <c r="F213" t="s">
-        <v>301</v>
+        <v>307</v>
+      </c>
+      <c r="G213" t="s">
+        <v>673</v>
       </c>
       <c r="H213" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="I213" t="s">
-        <v>628</v>
-      </c>
-      <c r="G213" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" ns3:dyDescent="0.25">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2026</v>
       </c>
       <c r="B214" t="s">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="C214" t="s">
-        <v>693</v>
+        <v>670</v>
       </c>
       <c r="D214" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="E214" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F214" t="s">
+        <v>81</v>
+      </c>
+      <c r="G214" t="s">
+        <v>185</v>
+      </c>
+      <c r="H214" t="s">
+        <v>381</v>
+      </c>
+      <c r="I214" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>2026</v>
+      </c>
+      <c r="B215" t="s">
+        <v>668</v>
+      </c>
+      <c r="C215" t="s">
+        <v>671</v>
+      </c>
+      <c r="D215" t="s">
+        <v>43</v>
+      </c>
+      <c r="E215" t="s">
+        <v>64</v>
+      </c>
+      <c r="F215" t="s">
         <v>49</v>
       </c>
-      <c r="H214" t="s">
-        <v>397</v>
-      </c>
-      <c r="I214" t="s">
-        <v>629</v>
-      </c>
-      <c r="G214" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A215">
-        <v>2026</v>
-      </c>
-      <c r="B215" t="s">
-        <v>687</v>
-      </c>
-      <c r="C215" t="s">
-        <v>690</v>
-      </c>
-      <c r="D215" t="s">
+      <c r="G215" t="s">
+        <v>672</v>
+      </c>
+      <c r="H215" t="s">
+        <v>376</v>
+      </c>
+      <c r="I215" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>2026</v>
+      </c>
+      <c r="B216" t="s">
+        <v>668</v>
+      </c>
+      <c r="C216" t="s">
+        <v>671</v>
+      </c>
+      <c r="D216" t="s">
         <v>9</v>
       </c>
-      <c r="E215" t="s">
+      <c r="E216" t="s">
         <v>97</v>
       </c>
-      <c r="F215" t="s">
-        <v>319</v>
-      </c>
-      <c r="H215" t="s">
-        <v>398</v>
-      </c>
-      <c r="I215" t="s">
-        <v>630</v>
-      </c>
-      <c r="G215" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" ns3:dyDescent="0.25">
-      <c r="A216">
-        <v>2026</v>
-      </c>
-      <c r="B216" t="s">
-        <v>687</v>
-      </c>
-      <c r="C216" t="s">
-        <v>689</v>
-      </c>
-      <c r="D216" t="s">
-        <v>80</v>
-      </c>
-      <c r="E216" t="s">
-        <v>48</v>
-      </c>
       <c r="F216" t="s">
-        <v>81</v>
+        <v>315</v>
+      </c>
+      <c r="G216" t="s">
+        <v>675</v>
       </c>
       <c r="H216" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="I216" t="s">
-        <v>631</v>
-      </c>
-      <c r="G216" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" ns3:dyDescent="0.25">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2026</v>
       </c>
       <c r="B217" t="s">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="C217" t="s">
-        <v>690</v>
+        <v>671</v>
       </c>
       <c r="D217" t="s">
         <v>96</v>
@@ -8812,16 +8756,16 @@
         <v>22</v>
       </c>
       <c r="F217" t="s">
-        <v>306</v>
-      </c>
-      <c r="H217" t="s">
-        <v>400</v>
-      </c>
-      <c r="I217" t="s">
-        <v>632</v>
+        <v>304</v>
       </c>
       <c r="G217" t="s">
         <v>35</v>
+      </c>
+      <c r="H217" t="s">
+        <v>382</v>
+      </c>
+      <c r="I217" t="s">
+        <v>614</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assets/assets/afl_fixtures_2026.xlsx
+++ b/docs/assets/assets/afl_fixtures_2026.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB1EFC8A-DC52-4305-BA12-001E6F269A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B6F09-94EA-4604-8ABA-60E488CD477F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="0" windowWidth="33120" windowHeight="20790" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
+    <workbookView xWindow="3120" yWindow="810" windowWidth="22440" windowHeight="20790" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="685">
   <si>
     <t>ROUND</t>
   </si>
@@ -2065,6 +2067,33 @@
   </si>
   <si>
     <t>3.20pm</t>
+  </si>
+  <si>
+    <t>Friday August 28</t>
+  </si>
+  <si>
+    <t>7:40pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9020</t>
+  </si>
+  <si>
+    <t>CD_M20260142502</t>
+  </si>
+  <si>
+    <t>Saturday August 29</t>
+  </si>
+  <si>
+    <t>7:35pm</t>
+  </si>
+  <si>
+    <t>CD_M20260142501</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9021</t>
+  </si>
+  <si>
+    <t>WF</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB6B02A0-21B2-418E-97BD-054996A22EC7}">
-  <dimension ref="A1:I217"/>
+  <dimension ref="A1:I219"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -8768,7 +8797,66 @@
         <v>614</v>
       </c>
     </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>2026</v>
+      </c>
+      <c r="B218" t="s">
+        <v>684</v>
+      </c>
+      <c r="C218" t="s">
+        <v>676</v>
+      </c>
+      <c r="D218" t="s">
+        <v>27</v>
+      </c>
+      <c r="E218" t="s">
+        <v>59</v>
+      </c>
+      <c r="F218" t="s">
+        <v>299</v>
+      </c>
+      <c r="G218" t="s">
+        <v>677</v>
+      </c>
+      <c r="H218" t="s">
+        <v>678</v>
+      </c>
+      <c r="I218" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>2026</v>
+      </c>
+      <c r="B219" t="s">
+        <v>684</v>
+      </c>
+      <c r="C219" t="s">
+        <v>680</v>
+      </c>
+      <c r="D219" t="s">
+        <v>67</v>
+      </c>
+      <c r="E219" t="s">
+        <v>39</v>
+      </c>
+      <c r="F219" t="s">
+        <v>299</v>
+      </c>
+      <c r="G219" t="s">
+        <v>681</v>
+      </c>
+      <c r="H219" t="s">
+        <v>683</v>
+      </c>
+      <c r="I219" t="s">
+        <v>682</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I1" xr:uid="{CB6B02A0-21B2-418E-97BD-054996A22EC7}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2:H10">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>

--- a/docs/assets/assets/afl_fixtures_2026.xlsx
+++ b/docs/assets/assets/afl_fixtures_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B6F09-94EA-4604-8ABA-60E488CD477F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA154F6-D252-4CA3-B2AE-8244C007BA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="810" windowWidth="22440" windowHeight="20790" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
+    <workbookView xWindow="2730" yWindow="810" windowWidth="22440" windowHeight="20790" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="702">
   <si>
     <t>ROUND</t>
   </si>
@@ -2093,7 +2093,58 @@
     <t>https://www.afl.com.au/afl/matches/9021</t>
   </si>
   <si>
+    <t>QE</t>
+  </si>
+  <si>
+    <t>Thursday September 3</t>
+  </si>
+  <si>
+    <t>Friday September 4</t>
+  </si>
+  <si>
+    <t>Saturday September 5</t>
+  </si>
+  <si>
+    <t>Hawthorn</t>
+  </si>
+  <si>
+    <t>8:10pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9024</t>
+  </si>
+  <si>
+    <t>CD_M20260142601</t>
+  </si>
+  <si>
+    <t>Brisbane Lions</t>
+  </si>
+  <si>
+    <t>SCG</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9029</t>
+  </si>
+  <si>
+    <t>CD_M20260142602</t>
+  </si>
+  <si>
     <t>WF</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9022</t>
+  </si>
+  <si>
+    <t>CD_M20260142603</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9025</t>
+  </si>
+  <si>
+    <t>CD_M20260142604</t>
   </si>
 </sst>
 </file>
@@ -2492,7 +2543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB6B02A0-21B2-418E-97BD-054996A22EC7}">
-  <dimension ref="A1:I219"/>
+  <dimension ref="A1:I223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -8802,7 +8853,7 @@
         <v>2026</v>
       </c>
       <c r="B218" t="s">
-        <v>684</v>
+        <v>697</v>
       </c>
       <c r="C218" t="s">
         <v>676</v>
@@ -8831,7 +8882,7 @@
         <v>2026</v>
       </c>
       <c r="B219" t="s">
-        <v>684</v>
+        <v>697</v>
       </c>
       <c r="C219" t="s">
         <v>680</v>
@@ -8853,6 +8904,122 @@
       </c>
       <c r="I219" t="s">
         <v>682</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>2026</v>
+      </c>
+      <c r="B220" t="s">
+        <v>684</v>
+      </c>
+      <c r="C220" t="s">
+        <v>685</v>
+      </c>
+      <c r="D220" t="s">
+        <v>88</v>
+      </c>
+      <c r="E220" t="s">
+        <v>688</v>
+      </c>
+      <c r="F220" t="s">
+        <v>304</v>
+      </c>
+      <c r="G220" t="s">
+        <v>689</v>
+      </c>
+      <c r="H220" t="s">
+        <v>690</v>
+      </c>
+      <c r="I220" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>2026</v>
+      </c>
+      <c r="B221" t="s">
+        <v>684</v>
+      </c>
+      <c r="C221" t="s">
+        <v>686</v>
+      </c>
+      <c r="D221" t="s">
+        <v>52</v>
+      </c>
+      <c r="E221" t="s">
+        <v>39</v>
+      </c>
+      <c r="F221" t="s">
+        <v>299</v>
+      </c>
+      <c r="G221" t="s">
+        <v>677</v>
+      </c>
+      <c r="H221" t="s">
+        <v>698</v>
+      </c>
+      <c r="I221" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>2026</v>
+      </c>
+      <c r="B222" t="s">
+        <v>684</v>
+      </c>
+      <c r="C222" t="s">
+        <v>687</v>
+      </c>
+      <c r="D222" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" t="s">
+        <v>692</v>
+      </c>
+      <c r="F222" t="s">
+        <v>693</v>
+      </c>
+      <c r="G222" t="s">
+        <v>694</v>
+      </c>
+      <c r="H222" t="s">
+        <v>695</v>
+      </c>
+      <c r="I222" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>2026</v>
+      </c>
+      <c r="B223" t="s">
+        <v>684</v>
+      </c>
+      <c r="C223" t="s">
+        <v>687</v>
+      </c>
+      <c r="D223" t="s">
+        <v>80</v>
+      </c>
+      <c r="E223" t="s">
+        <v>27</v>
+      </c>
+      <c r="F223" t="s">
+        <v>81</v>
+      </c>
+      <c r="G223" t="s">
+        <v>681</v>
+      </c>
+      <c r="H223" t="s">
+        <v>700</v>
+      </c>
+      <c r="I223" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assets/assets/afl_fixtures_2026.xlsx
+++ b/docs/assets/assets/afl_fixtures_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA154F6-D252-4CA3-B2AE-8244C007BA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D80606-01F1-444A-8444-73539BF28417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="810" windowWidth="22440" windowHeight="20790" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="709">
   <si>
     <t>ROUND</t>
   </si>
@@ -2096,6 +2096,9 @@
     <t>QE</t>
   </si>
   <si>
+    <t>SF</t>
+  </si>
+  <si>
     <t>Thursday September 3</t>
   </si>
   <si>
@@ -2145,6 +2148,24 @@
   </si>
   <si>
     <t>CD_M20260142604</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9023</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9030</t>
+  </si>
+  <si>
+    <t>Friday September 11</t>
+  </si>
+  <si>
+    <t>CD_M20260142701</t>
+  </si>
+  <si>
+    <t>Saturday September 12</t>
+  </si>
+  <si>
+    <t>CD_M20260142702</t>
   </si>
 </sst>
 </file>
@@ -2543,7 +2564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB6B02A0-21B2-418E-97BD-054996A22EC7}">
-  <dimension ref="A1:I223"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -8853,7 +8874,7 @@
         <v>2026</v>
       </c>
       <c r="B218" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C218" t="s">
         <v>676</v>
@@ -8882,7 +8903,7 @@
         <v>2026</v>
       </c>
       <c r="B219" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C219" t="s">
         <v>680</v>
@@ -8914,25 +8935,25 @@
         <v>684</v>
       </c>
       <c r="C220" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D220" t="s">
         <v>88</v>
       </c>
       <c r="E220" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F220" t="s">
         <v>304</v>
       </c>
       <c r="G220" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H220" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I220" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -8943,7 +8964,7 @@
         <v>684</v>
       </c>
       <c r="C221" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D221" t="s">
         <v>52</v>
@@ -8958,10 +8979,10 @@
         <v>677</v>
       </c>
       <c r="H221" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I221" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -8972,25 +8993,25 @@
         <v>684</v>
       </c>
       <c r="C222" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
       </c>
       <c r="E222" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F222" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G222" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H222" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I222" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -9001,7 +9022,7 @@
         <v>684</v>
       </c>
       <c r="C223" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D223" t="s">
         <v>80</v>
@@ -9016,10 +9037,68 @@
         <v>681</v>
       </c>
       <c r="H223" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I223" t="s">
-        <v>701</v>
+        <v>702</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>2026</v>
+      </c>
+      <c r="B224" t="s">
+        <v>685</v>
+      </c>
+      <c r="C224" t="s">
+        <v>705</v>
+      </c>
+      <c r="D224" t="s">
+        <v>88</v>
+      </c>
+      <c r="E224" t="s">
+        <v>52</v>
+      </c>
+      <c r="F224" t="s">
+        <v>304</v>
+      </c>
+      <c r="G224" t="s">
+        <v>690</v>
+      </c>
+      <c r="H224" t="s">
+        <v>703</v>
+      </c>
+      <c r="I224" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>2026</v>
+      </c>
+      <c r="B225" t="s">
+        <v>685</v>
+      </c>
+      <c r="C225" t="s">
+        <v>707</v>
+      </c>
+      <c r="D225" t="s">
+        <v>693</v>
+      </c>
+      <c r="E225" t="s">
+        <v>80</v>
+      </c>
+      <c r="F225" t="s">
+        <v>296</v>
+      </c>
+      <c r="G225" t="s">
+        <v>681</v>
+      </c>
+      <c r="H225" t="s">
+        <v>704</v>
+      </c>
+      <c r="I225" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>
